--- a/data/italy/p4_modeling/2024-10-12/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-12/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,22 +537,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>25</v>
+        <v>273</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.29383869787502</v>
+        <v>1.896126162039457</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5779623475030555</v>
+        <v>38.49424690732052</v>
       </c>
       <c r="D2" t="n">
-        <v>1.842682869246092</v>
+        <v>66.38692321761452</v>
       </c>
       <c r="E2" t="n">
-        <v>331.0515237994687</v>
+        <v>8926.047053286706</v>
       </c>
       <c r="F2" t="n">
-        <v>2.018606852435785</v>
+        <v>54.42711617857747</v>
       </c>
       <c r="G2" t="n">
         <v>-0.25</v>
@@ -562,18 +562,22 @@
           <t>kelly</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(164, 31)</t>
+          <t>(164, 65)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -582,7 +586,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.492626917924119</v>
+        <v>0.4139026101645065</v>
       </c>
       <c r="O2" t="n">
         <v>60</v>
@@ -594,39 +598,39 @@
         <v>46</v>
       </c>
       <c r="R2" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="S2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V2" t="n">
-        <v>45.73170731707317</v>
+        <v>46.34146341463415</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4183903751825488</v>
+        <v>-0.4266336300959819</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2323702533209567</v>
+        <v>3.629643118479962</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5397711384304424</v>
+        <v>7.435290830037892</v>
       </c>
       <c r="E3" t="n">
-        <v>71.68923038730804</v>
+        <v>1677.369356037947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4371294535811466</v>
+        <v>10.22786192706065</v>
       </c>
       <c r="G3" t="n">
         <v>-0.35</v>
@@ -636,18 +640,22 @@
           <t>kelly</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(164, 25)</t>
+          <t>(164, 77)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -656,45 +664,51 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.8811764730374949</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>1.817869854748674</v>
+      </c>
+      <c r="O3" t="n">
+        <v>60</v>
+      </c>
+      <c r="P3" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>46</v>
+      </c>
       <c r="R3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="S3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="V3" t="n">
-        <v>43.29268292682926</v>
+        <v>48.17073170731707</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.6889365617839698</v>
+        <v>-1.727514626572671</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2663784624785005</v>
+        <v>0.03854900004475709</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7787588956499777</v>
+        <v>2.720145318314576</v>
       </c>
       <c r="E4" t="n">
-        <v>57.78770750570732</v>
+        <v>498.3527358038604</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3523640701567519</v>
+        <v>3.038736193925978</v>
       </c>
       <c r="G4" t="n">
         <v>-0.25</v>
@@ -704,18 +718,22 @@
           <t>kelly</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(164, 34)</t>
+          <t>(164, 65)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -724,45 +742,51 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.3227948944453096</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>77.82788633681471</v>
+      </c>
+      <c r="O4" t="n">
+        <v>60</v>
+      </c>
+      <c r="P4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>46</v>
+      </c>
       <c r="R4" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="S4" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="T4" t="n">
         <v>23</v>
       </c>
       <c r="U4" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="V4" t="n">
-        <v>43.29268292682926</v>
+        <v>45.1219512195122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>12</v>
+        <v>259</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.627819056574129</v>
+        <v>-1.606736920625837</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3038149578046913</v>
+        <v>2.104552613251398</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5295770827090096</v>
+        <v>3.329034859606559</v>
       </c>
       <c r="E5" t="n">
-        <v>56.5375202930687</v>
+        <v>423.2870124604217</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3447409773967604</v>
+        <v>2.581018368661108</v>
       </c>
       <c r="G5" t="n">
         <v>-0.25</v>
@@ -772,18 +796,22 @@
           <t>kelly</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(164, 37)</t>
+          <t>(164, 65)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -792,19 +820,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.134707059480523</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>0.2263976449957225</v>
+      </c>
+      <c r="O5" t="n">
+        <v>60</v>
+      </c>
+      <c r="P5" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>46</v>
+      </c>
       <c r="R5" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="S5" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="T5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U5" t="n">
         <v>75</v>
@@ -815,43 +849,47 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>5</v>
+        <v>431</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2707332259722691</v>
+        <v>-0.9436616023377979</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2232582881700093</v>
+        <v>1.270713017851595</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3948171343930221</v>
+        <v>2.003201850243622</v>
       </c>
       <c r="E6" t="n">
-        <v>40.49978963121458</v>
+        <v>409.4509320684475</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2469499367756987</v>
+        <v>2.496652024807607</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>kelly</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(164, 17)</t>
+          <t>(164, 67)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -860,93 +898,4711 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.106117666671566</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+        <v>0.9647646555386021</v>
+      </c>
+      <c r="O6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P6" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>46</v>
+      </c>
       <c r="R6" t="n">
         <v>58</v>
       </c>
       <c r="S6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="T6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U6" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="V6" t="n">
-        <v>42.07317073170731</v>
+        <v>44.51219512195122</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-1.393589147382974</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.909588996726958</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.065686008597786</v>
+      </c>
+      <c r="E7" t="n">
+        <v>344.7092103495053</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.101885428960399</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>(164, 8)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1007004295495195</v>
+      </c>
+      <c r="O7" t="n">
+        <v>60</v>
+      </c>
+      <c r="P7" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>46</v>
+      </c>
+      <c r="R7" t="n">
+        <v>67</v>
+      </c>
+      <c r="S7" t="n">
+        <v>77</v>
+      </c>
+      <c r="T7" t="n">
+        <v>20</v>
+      </c>
+      <c r="U7" t="n">
+        <v>74</v>
+      </c>
+      <c r="V7" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-1.29383869787502</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5779623475030555</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.842682869246092</v>
+      </c>
+      <c r="E8" t="n">
+        <v>331.0515237994687</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.018606852435785</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>(164, 31)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2.492626917924118</v>
+      </c>
+      <c r="O8" t="n">
+        <v>60</v>
+      </c>
+      <c r="P8" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>46</v>
+      </c>
+      <c r="R8" t="n">
+        <v>72</v>
+      </c>
+      <c r="S8" t="n">
+        <v>78</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U8" t="n">
+        <v>75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>45.73170731707317</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-1.270711100532256</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1992282837143054</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.053024831311012</v>
+      </c>
+      <c r="E9" t="n">
+        <v>228.3952213169126</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.39265378851776</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>(164, 42)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5.990241358073606</v>
+      </c>
+      <c r="O9" t="n">
+        <v>60</v>
+      </c>
+      <c r="P9" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>46</v>
+      </c>
+      <c r="R9" t="n">
+        <v>72</v>
+      </c>
+      <c r="S9" t="n">
+        <v>68</v>
+      </c>
+      <c r="T9" t="n">
+        <v>24</v>
+      </c>
+      <c r="U9" t="n">
+        <v>76</v>
+      </c>
+      <c r="V9" t="n">
+        <v>46.34146341463415</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>359</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.281603424354408</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.08088815800616288</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.437106167280731</v>
+      </c>
+      <c r="E10" t="n">
+        <v>189.3215640517438</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.154399780803316</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>(164, 39)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>13.27155481418382</v>
+      </c>
+      <c r="O10" t="n">
+        <v>60</v>
+      </c>
+      <c r="P10" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>46</v>
+      </c>
+      <c r="R10" t="n">
+        <v>74</v>
+      </c>
+      <c r="S10" t="n">
+        <v>72</v>
+      </c>
+      <c r="T10" t="n">
+        <v>18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>76</v>
+      </c>
+      <c r="V10" t="n">
+        <v>46.34146341463415</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.863279229568991</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.6045860133527742</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7938181292726201</v>
+      </c>
+      <c r="E11" t="n">
+        <v>169.9763727180111</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.036441297061043</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>(164, 50)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2.71429916367629</v>
+      </c>
+      <c r="O11" t="n">
+        <v>60</v>
+      </c>
+      <c r="P11" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>46</v>
+      </c>
+      <c r="R11" t="n">
+        <v>80</v>
+      </c>
+      <c r="S11" t="n">
+        <v>65</v>
+      </c>
+      <c r="T11" t="n">
+        <v>19</v>
+      </c>
+      <c r="U11" t="n">
+        <v>75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>45.73170731707317</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.9159825864001954</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5754312203429623</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6954712754722374</v>
+      </c>
+      <c r="E12" t="n">
+        <v>125.6449291941915</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7661276170377531</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>(164, 29)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3313973763556554</v>
+      </c>
+      <c r="O12" t="n">
+        <v>60</v>
+      </c>
+      <c r="P12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>46</v>
+      </c>
+      <c r="R12" t="n">
+        <v>70</v>
+      </c>
+      <c r="S12" t="n">
+        <v>84</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U12" t="n">
+        <v>72</v>
+      </c>
+      <c r="V12" t="n">
+        <v>43.90243902439025</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.1025706956479567</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.08963819641877152</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8355662296590918</v>
+      </c>
+      <c r="E13" t="n">
+        <v>116.903222141034</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7128245252502073</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>(164, 77)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>6.952240827336992</v>
+      </c>
+      <c r="O13" t="n">
+        <v>60</v>
+      </c>
+      <c r="P13" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>46</v>
+      </c>
+      <c r="R13" t="n">
+        <v>68</v>
+      </c>
+      <c r="S13" t="n">
+        <v>84</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" t="n">
+        <v>74</v>
+      </c>
+      <c r="V13" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.7308108907700976</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2101749345543382</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4838986556992986</v>
+      </c>
+      <c r="E14" t="n">
+        <v>115.0545731115202</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.701552275070245</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>(164, 22)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2.337944539189886</v>
+      </c>
+      <c r="O14" t="n">
+        <v>60</v>
+      </c>
+      <c r="P14" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>46</v>
+      </c>
+      <c r="R14" t="n">
+        <v>83</v>
+      </c>
+      <c r="S14" t="n">
+        <v>70</v>
+      </c>
+      <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>76</v>
+      </c>
+      <c r="V14" t="n">
+        <v>46.34146341463415</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.08541661905859144</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6368493526320452</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5886110665875751</v>
+      </c>
+      <c r="E15" t="n">
+        <v>108.0236596256396</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6586808513758512</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>(164, 51)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0.03428047567855444</v>
+      </c>
+      <c r="O15" t="n">
+        <v>60</v>
+      </c>
+      <c r="P15" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>46</v>
+      </c>
+      <c r="R15" t="n">
+        <v>81</v>
+      </c>
+      <c r="S15" t="n">
+        <v>62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>21</v>
+      </c>
+      <c r="U15" t="n">
+        <v>79</v>
+      </c>
+      <c r="V15" t="n">
+        <v>48.17073170731707</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.7872862624629369</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.00830850585574467</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7738854644366558</v>
+      </c>
+      <c r="E16" t="n">
+        <v>107.3044152880446</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6542952151710039</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>(164, 47)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>79.75004561964784</v>
+      </c>
+      <c r="O16" t="n">
+        <v>60</v>
+      </c>
+      <c r="P16" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>46</v>
+      </c>
+      <c r="R16" t="n">
+        <v>64</v>
+      </c>
+      <c r="S16" t="n">
+        <v>76</v>
+      </c>
+      <c r="T16" t="n">
+        <v>24</v>
+      </c>
+      <c r="U16" t="n">
+        <v>74</v>
+      </c>
+      <c r="V16" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>411</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.202522073267674</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3114694487797945</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3659698589989949</v>
+      </c>
+      <c r="E17" t="n">
+        <v>95.44078115492562</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5819559826519854</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>(164, 23)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8684207550109417</v>
+      </c>
+      <c r="O17" t="n">
+        <v>60</v>
+      </c>
+      <c r="P17" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>46</v>
+      </c>
+      <c r="R17" t="n">
+        <v>70</v>
+      </c>
+      <c r="S17" t="n">
+        <v>74</v>
+      </c>
+      <c r="T17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U17" t="n">
+        <v>72</v>
+      </c>
+      <c r="V17" t="n">
+        <v>43.90243902439025</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>391</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.8084740289345299</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2472274703035632</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1173185206593994</v>
+      </c>
+      <c r="E18" t="n">
+        <v>85.55547355762971</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5216797168148153</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>(164, 43)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1.110120352622063</v>
+      </c>
+      <c r="O18" t="n">
+        <v>60</v>
+      </c>
+      <c r="P18" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>46</v>
+      </c>
+      <c r="R18" t="n">
+        <v>72</v>
+      </c>
+      <c r="S18" t="n">
+        <v>70</v>
+      </c>
+      <c r="T18" t="n">
         <v>22</v>
       </c>
-      <c r="B7" t="n">
+      <c r="U18" t="n">
+        <v>69</v>
+      </c>
+      <c r="V18" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5387685651725178</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2575614088561794</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6152593578413085</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85.46893504322568</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5211520429464981</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>(164, 17)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>3.023408884354667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>60</v>
+      </c>
+      <c r="P19" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>46</v>
+      </c>
+      <c r="R19" t="n">
+        <v>61</v>
+      </c>
+      <c r="S19" t="n">
+        <v>81</v>
+      </c>
+      <c r="T19" t="n">
+        <v>22</v>
+      </c>
+      <c r="U19" t="n">
+        <v>74</v>
+      </c>
+      <c r="V19" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.6864414057829122</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3902779398667633</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5597692970039736</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78.55616861720677</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4790010281536998</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>(164, 49)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2273330855370037</v>
+      </c>
+      <c r="O20" t="n">
+        <v>60</v>
+      </c>
+      <c r="P20" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>46</v>
+      </c>
+      <c r="R20" t="n">
+        <v>65</v>
+      </c>
+      <c r="S20" t="n">
+        <v>84</v>
+      </c>
+      <c r="T20" t="n">
+        <v>15</v>
+      </c>
+      <c r="U20" t="n">
+        <v>69</v>
+      </c>
+      <c r="V20" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>373</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.6495371033671955</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.01258303421742198</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.365304195919043</v>
+      </c>
+      <c r="E21" t="n">
+        <v>74.92421641985342</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4568549781698379</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>(164, 39)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>37.30721893271928</v>
+      </c>
+      <c r="O21" t="n">
+        <v>60</v>
+      </c>
+      <c r="P21" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>46</v>
+      </c>
+      <c r="R21" t="n">
+        <v>72</v>
+      </c>
+      <c r="S21" t="n">
+        <v>80</v>
+      </c>
+      <c r="T21" t="n">
+        <v>12</v>
+      </c>
+      <c r="U21" t="n">
+        <v>75</v>
+      </c>
+      <c r="V21" t="n">
+        <v>45.73170731707317</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.4183903751825488</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.2323702533209567</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5397711384304424</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71.68923038730804</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4371294535811466</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>(164, 25)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8811764730374951</v>
+      </c>
+      <c r="O22" t="n">
+        <v>60</v>
+      </c>
+      <c r="P22" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>46</v>
+      </c>
+      <c r="R22" t="n">
+        <v>63</v>
+      </c>
+      <c r="S22" t="n">
+        <v>84</v>
+      </c>
+      <c r="T22" t="n">
+        <v>17</v>
+      </c>
+      <c r="U22" t="n">
+        <v>71</v>
+      </c>
+      <c r="V22" t="n">
+        <v>43.29268292682926</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-1.298445540844414</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.1426574248687518</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5110236516481954</v>
+      </c>
+      <c r="E23" t="n">
+        <v>71.51708348233416</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.4360797773313058</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>(164, 47)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>4.056831971644725</v>
+      </c>
+      <c r="O23" t="n">
+        <v>60</v>
+      </c>
+      <c r="P23" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>46</v>
+      </c>
+      <c r="R23" t="n">
+        <v>78</v>
+      </c>
+      <c r="S23" t="n">
+        <v>65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>21</v>
+      </c>
+      <c r="U23" t="n">
+        <v>69</v>
+      </c>
+      <c r="V23" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.7590930908186222</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.201545842318864</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.3256250402432596</v>
+      </c>
+      <c r="E24" t="n">
+        <v>68.81743421479914</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.4196185013097508</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>(164, 58)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3.082000285800368</v>
+      </c>
+      <c r="O24" t="n">
+        <v>60</v>
+      </c>
+      <c r="P24" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>46</v>
+      </c>
+      <c r="R24" t="n">
+        <v>72</v>
+      </c>
+      <c r="S24" t="n">
+        <v>79</v>
+      </c>
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>73</v>
+      </c>
+      <c r="V24" t="n">
+        <v>44.51219512195122</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.3018470033094539</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.0184048499194067</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4886607761800034</v>
+      </c>
+      <c r="E25" t="n">
+        <v>68.35783628181818</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4168160748891352</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>(164, 48)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>23.64707817310861</v>
+      </c>
+      <c r="O25" t="n">
+        <v>60</v>
+      </c>
+      <c r="P25" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>46</v>
+      </c>
+      <c r="R25" t="n">
+        <v>65</v>
+      </c>
+      <c r="S25" t="n">
+        <v>88</v>
+      </c>
+      <c r="T25" t="n">
+        <v>11</v>
+      </c>
+      <c r="U25" t="n">
+        <v>71</v>
+      </c>
+      <c r="V25" t="n">
+        <v>43.29268292682926</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.1772591716471172</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.08916231945623763</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.2958123020600122</v>
+      </c>
+      <c r="E26" t="n">
+        <v>67.64450599438334</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4124664999657521</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>(164, 30)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>5.626018058763012</v>
+      </c>
+      <c r="O26" t="n">
+        <v>60</v>
+      </c>
+      <c r="P26" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>46</v>
+      </c>
+      <c r="R26" t="n">
+        <v>76</v>
+      </c>
+      <c r="S26" t="n">
+        <v>77</v>
+      </c>
+      <c r="T26" t="n">
+        <v>11</v>
+      </c>
+      <c r="U26" t="n">
+        <v>74</v>
+      </c>
+      <c r="V26" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>407</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-1.23038361130531</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.1951992963691856</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1187709119949317</v>
+      </c>
+      <c r="E27" t="n">
+        <v>66.93106740716465</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4081162646778332</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>(164, 67)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>3.090767089169995</v>
+      </c>
+      <c r="O27" t="n">
+        <v>60</v>
+      </c>
+      <c r="P27" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>46</v>
+      </c>
+      <c r="R27" t="n">
+        <v>64</v>
+      </c>
+      <c r="S27" t="n">
+        <v>81</v>
+      </c>
+      <c r="T27" t="n">
+        <v>19</v>
+      </c>
+      <c r="U27" t="n">
+        <v>73</v>
+      </c>
+      <c r="V27" t="n">
+        <v>44.51219512195122</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-1.201143692429389</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.08932629065833851</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5501876732815073</v>
+      </c>
+      <c r="E28" t="n">
+        <v>60.67921570260708</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3699952176988237</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>(164, 44)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>3.142064054960117</v>
+      </c>
+      <c r="O28" t="n">
+        <v>60</v>
+      </c>
+      <c r="P28" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>46</v>
+      </c>
+      <c r="R28" t="n">
+        <v>91</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="n">
+        <v>23</v>
+      </c>
+      <c r="U28" t="n">
+        <v>73</v>
+      </c>
+      <c r="V28" t="n">
+        <v>44.51219512195122</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>415</v>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.3824306631146794</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.3509124580478499</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3558019892225991</v>
+      </c>
+      <c r="E29" t="n">
+        <v>60.39887618210983</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3682858303787185</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>(164, 43)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0.04950913520573728</v>
+      </c>
+      <c r="O29" t="n">
+        <v>60</v>
+      </c>
+      <c r="P29" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>46</v>
+      </c>
+      <c r="R29" t="n">
+        <v>68</v>
+      </c>
+      <c r="S29" t="n">
+        <v>76</v>
+      </c>
+      <c r="T29" t="n">
+        <v>20</v>
+      </c>
+      <c r="U29" t="n">
+        <v>71</v>
+      </c>
+      <c r="V29" t="n">
+        <v>43.29268292682926</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>431</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.758487333493334</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.2820740912587257</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.05688237791939372</v>
+      </c>
+      <c r="E30" t="n">
+        <v>58.23946200138621</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3551186707401598</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>(164, 67)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2.258955294885398</v>
+      </c>
+      <c r="O30" t="n">
+        <v>60</v>
+      </c>
+      <c r="P30" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>46</v>
+      </c>
+      <c r="R30" t="n">
+        <v>72</v>
+      </c>
+      <c r="S30" t="n">
+        <v>81</v>
+      </c>
+      <c r="T30" t="n">
+        <v>11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>74</v>
+      </c>
+      <c r="V30" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.6889365617839698</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.2663784624785005</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.7787588956499777</v>
+      </c>
+      <c r="E31" t="n">
+        <v>57.78770750570732</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3523640701567519</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>(164, 34)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0.3227948944453096</v>
+      </c>
+      <c r="O31" t="n">
+        <v>60</v>
+      </c>
+      <c r="P31" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>46</v>
+      </c>
+      <c r="R31" t="n">
+        <v>69</v>
+      </c>
+      <c r="S31" t="n">
+        <v>72</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23</v>
+      </c>
+      <c r="U31" t="n">
+        <v>71</v>
+      </c>
+      <c r="V31" t="n">
+        <v>43.29268292682926</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.627819056574129</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.3038149578046913</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.5295770827090096</v>
+      </c>
+      <c r="E32" t="n">
+        <v>56.5375202930687</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3447409773967604</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>(164, 37)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2.134707059480523</v>
+      </c>
+      <c r="O32" t="n">
+        <v>60</v>
+      </c>
+      <c r="P32" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>46</v>
+      </c>
+      <c r="R32" t="n">
+        <v>92</v>
+      </c>
+      <c r="S32" t="n">
+        <v>59</v>
+      </c>
+      <c r="T32" t="n">
+        <v>13</v>
+      </c>
+      <c r="U32" t="n">
+        <v>75</v>
+      </c>
+      <c r="V32" t="n">
+        <v>45.73170731707317</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.9665070146464771</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.2969809755969115</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1945905772476886</v>
+      </c>
+      <c r="E33" t="n">
+        <v>54.16908295296221</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.3302992862985501</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>(164, 15)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0.1121900506746975</v>
+      </c>
+      <c r="O33" t="n">
+        <v>60</v>
+      </c>
+      <c r="P33" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>46</v>
+      </c>
+      <c r="R33" t="n">
+        <v>69</v>
+      </c>
+      <c r="S33" t="n">
+        <v>81</v>
+      </c>
+      <c r="T33" t="n">
+        <v>14</v>
+      </c>
+      <c r="U33" t="n">
+        <v>67</v>
+      </c>
+      <c r="V33" t="n">
+        <v>40.85365853658536</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.116191777450309</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1937545989322405</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.2778178409719161</v>
+      </c>
+      <c r="E34" t="n">
+        <v>52.15794631164721</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3180362579978488</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>(164, 65)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0.6414384987531158</v>
+      </c>
+      <c r="O34" t="n">
+        <v>60</v>
+      </c>
+      <c r="P34" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>46</v>
+      </c>
+      <c r="R34" t="n">
+        <v>75</v>
+      </c>
+      <c r="S34" t="n">
+        <v>53</v>
+      </c>
+      <c r="T34" t="n">
+        <v>36</v>
+      </c>
+      <c r="U34" t="n">
+        <v>80</v>
+      </c>
+      <c r="V34" t="n">
+        <v>48.78048780487805</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>405</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.9132125350257122</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.2641651603330276</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.2188344244153796</v>
+      </c>
+      <c r="E35" t="n">
+        <v>47.42561091383718</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2891805543526657</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>(164, 89)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0.09469603784277139</v>
+      </c>
+      <c r="O35" t="n">
+        <v>60</v>
+      </c>
+      <c r="P35" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>46</v>
+      </c>
+      <c r="R35" t="n">
+        <v>65</v>
+      </c>
+      <c r="S35" t="n">
+        <v>77</v>
+      </c>
+      <c r="T35" t="n">
+        <v>22</v>
+      </c>
+      <c r="U35" t="n">
+        <v>75</v>
+      </c>
+      <c r="V35" t="n">
+        <v>45.73170731707317</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.7077620915048203</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.3596212123102464</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3817346293701274</v>
+      </c>
+      <c r="E36" t="n">
+        <v>46.88447072089011</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2858809190298177</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>(164, 47)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1.794950100950072</v>
+      </c>
+      <c r="O36" t="n">
+        <v>60</v>
+      </c>
+      <c r="P36" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>46</v>
+      </c>
+      <c r="R36" t="n">
+        <v>78</v>
+      </c>
+      <c r="S36" t="n">
+        <v>56</v>
+      </c>
+      <c r="T36" t="n">
+        <v>30</v>
+      </c>
+      <c r="U36" t="n">
+        <v>78</v>
+      </c>
+      <c r="V36" t="n">
+        <v>47.5609756097561</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.4192317647678772</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.2087440871096699</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.531386164383319</v>
+      </c>
+      <c r="E37" t="n">
+        <v>45.91862683516746</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.279991627043704</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>(164, 21)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2.34131524835289</v>
+      </c>
+      <c r="O37" t="n">
+        <v>60</v>
+      </c>
+      <c r="P37" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>46</v>
+      </c>
+      <c r="R37" t="n">
+        <v>69</v>
+      </c>
+      <c r="S37" t="n">
+        <v>80</v>
+      </c>
+      <c r="T37" t="n">
+        <v>15</v>
+      </c>
+      <c r="U37" t="n">
+        <v>70</v>
+      </c>
+      <c r="V37" t="n">
+        <v>42.68292682926829</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>393</v>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.4671086716976984</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1146961027714308</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.3670367141999942</v>
+      </c>
+      <c r="E38" t="n">
+        <v>45.15764492009609</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2753514934152201</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>(164, 29)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1.400704878037115</v>
+      </c>
+      <c r="O38" t="n">
+        <v>60</v>
+      </c>
+      <c r="P38" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>46</v>
+      </c>
+      <c r="R38" t="n">
+        <v>75</v>
+      </c>
+      <c r="S38" t="n">
+        <v>66</v>
+      </c>
+      <c r="T38" t="n">
+        <v>23</v>
+      </c>
+      <c r="U38" t="n">
+        <v>71</v>
+      </c>
+      <c r="V38" t="n">
+        <v>43.29268292682926</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.4251678065433589</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.2366028533725871</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.2458276139207142</v>
+      </c>
+      <c r="E39" t="n">
+        <v>43.55352075366494</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.265570248497957</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>(164, 16)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0.1224304555607105</v>
+      </c>
+      <c r="O39" t="n">
+        <v>60</v>
+      </c>
+      <c r="P39" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>46</v>
+      </c>
+      <c r="R39" t="n">
+        <v>69</v>
+      </c>
+      <c r="S39" t="n">
+        <v>73</v>
+      </c>
+      <c r="T39" t="n">
+        <v>22</v>
+      </c>
+      <c r="U39" t="n">
+        <v>67</v>
+      </c>
+      <c r="V39" t="n">
+        <v>40.85365853658536</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.2707332259722691</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.2232582881700093</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3948171343930221</v>
+      </c>
+      <c r="E40" t="n">
+        <v>40.49978963121458</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2469499367756987</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>(164, 17)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>2.106117666671566</v>
+      </c>
+      <c r="O40" t="n">
+        <v>60</v>
+      </c>
+      <c r="P40" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>46</v>
+      </c>
+      <c r="R40" t="n">
+        <v>58</v>
+      </c>
+      <c r="S40" t="n">
+        <v>87</v>
+      </c>
+      <c r="T40" t="n">
+        <v>19</v>
+      </c>
+      <c r="U40" t="n">
+        <v>69</v>
+      </c>
+      <c r="V40" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B41" t="n">
+        <v>-0.3735886662604463</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2211429387574934</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3835664364271457</v>
+      </c>
+      <c r="E41" t="n">
+        <v>38.76953839840019</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2363996243804889</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>(164, 22)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0.06899015500434375</v>
+      </c>
+      <c r="O41" t="n">
+        <v>60</v>
+      </c>
+      <c r="P41" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>46</v>
+      </c>
+      <c r="R41" t="n">
+        <v>63</v>
+      </c>
+      <c r="S41" t="n">
+        <v>77</v>
+      </c>
+      <c r="T41" t="n">
+        <v>24</v>
+      </c>
+      <c r="U41" t="n">
+        <v>70</v>
+      </c>
+      <c r="V41" t="n">
+        <v>42.68292682926829</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B42" t="n">
+        <v>-1.214087270241895</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.06527952905788922</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.4317663856781094</v>
+      </c>
+      <c r="E42" t="n">
+        <v>35.95596156410394</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.2192436680738045</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>(164, 14)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>4.358536301317087</v>
+      </c>
+      <c r="O42" t="n">
+        <v>60</v>
+      </c>
+      <c r="P42" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>46</v>
+      </c>
+      <c r="R42" t="n">
+        <v>63</v>
+      </c>
+      <c r="S42" t="n">
+        <v>77</v>
+      </c>
+      <c r="T42" t="n">
+        <v>24</v>
+      </c>
+      <c r="U42" t="n">
+        <v>67</v>
+      </c>
+      <c r="V42" t="n">
+        <v>40.85365853658536</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B43" t="n">
+        <v>-1.015718323821463</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.2801829888464317</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1307557621807462</v>
+      </c>
+      <c r="E43" t="n">
+        <v>34.30186506401921</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.2091577138049952</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>(164, 8)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1.74650397108739</v>
+      </c>
+      <c r="O43" t="n">
+        <v>60</v>
+      </c>
+      <c r="P43" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>46</v>
+      </c>
+      <c r="R43" t="n">
+        <v>72</v>
+      </c>
+      <c r="S43" t="n">
+        <v>69</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23</v>
+      </c>
+      <c r="U43" t="n">
+        <v>70</v>
+      </c>
+      <c r="V43" t="n">
+        <v>42.68292682926829</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>407</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.00737776448490763</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.2337974436379267</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.07696117327230088</v>
+      </c>
+      <c r="E44" t="n">
+        <v>29.01492380239969</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.176920267087803</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>(164, 67)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>1.756724557526783</v>
+      </c>
+      <c r="O44" t="n">
+        <v>60</v>
+      </c>
+      <c r="P44" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>46</v>
+      </c>
+      <c r="R44" t="n">
+        <v>75</v>
+      </c>
+      <c r="S44" t="n">
+        <v>37</v>
+      </c>
+      <c r="T44" t="n">
+        <v>52</v>
+      </c>
+      <c r="U44" t="n">
+        <v>74</v>
+      </c>
+      <c r="V44" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B45" t="n">
+        <v>-0.8465305504779401</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.1186060181914459</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.1751898995283771</v>
+      </c>
+      <c r="E45" t="n">
+        <v>28.77418107980824</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1754523236573673</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>(164, 17)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0.4792868551928276</v>
+      </c>
+      <c r="O45" t="n">
+        <v>60</v>
+      </c>
+      <c r="P45" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>46</v>
+      </c>
+      <c r="R45" t="n">
+        <v>68</v>
+      </c>
+      <c r="S45" t="n">
+        <v>84</v>
+      </c>
+      <c r="T45" t="n">
+        <v>12</v>
+      </c>
+      <c r="U45" t="n">
+        <v>69</v>
+      </c>
+      <c r="V45" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B46" t="n">
+        <v>-0.9261812924335178</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.06527727279216634</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.05791706187807686</v>
+      </c>
+      <c r="E46" t="n">
+        <v>27.01826435410063</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1647455143542721</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>(164, 72)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>3.52378059479903</v>
+      </c>
+      <c r="O46" t="n">
+        <v>60</v>
+      </c>
+      <c r="P46" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>46</v>
+      </c>
+      <c r="R46" t="n">
+        <v>75</v>
+      </c>
+      <c r="S46" t="n">
+        <v>70</v>
+      </c>
+      <c r="T46" t="n">
+        <v>19</v>
+      </c>
+      <c r="U46" t="n">
+        <v>69</v>
+      </c>
+      <c r="V46" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B47" t="n">
+        <v>-0.8285933157912795</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.1033647087916408</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2955218143331052</v>
+      </c>
+      <c r="E47" t="n">
+        <v>26.74556389907136</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.1630827067016546</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>(164, 15)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>2.577740687398359</v>
+      </c>
+      <c r="O47" t="n">
+        <v>60</v>
+      </c>
+      <c r="P47" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>46</v>
+      </c>
+      <c r="R47" t="n">
+        <v>66</v>
+      </c>
+      <c r="S47" t="n">
+        <v>85</v>
+      </c>
+      <c r="T47" t="n">
+        <v>13</v>
+      </c>
+      <c r="U47" t="n">
+        <v>70</v>
+      </c>
+      <c r="V47" t="n">
+        <v>42.68292682926829</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B48" t="n">
+        <v>-1.068636691651434</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.1200971810313662</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.1888853365347014</v>
+      </c>
+      <c r="E48" t="n">
+        <v>22.93456811659929</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1398449275402396</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>(164, 33)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0.1644313908060492</v>
+      </c>
+      <c r="O48" t="n">
+        <v>60</v>
+      </c>
+      <c r="P48" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>46</v>
+      </c>
+      <c r="R48" t="n">
+        <v>72</v>
+      </c>
+      <c r="S48" t="n">
+        <v>76</v>
+      </c>
+      <c r="T48" t="n">
+        <v>16</v>
+      </c>
+      <c r="U48" t="n">
+        <v>69</v>
+      </c>
+      <c r="V48" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B49" t="n">
+        <v>-0.7703581834752598</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.03225979211743109</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0828623119931539</v>
+      </c>
+      <c r="E49" t="n">
+        <v>22.84652948477256</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1393081066144668</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>(164, 53)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>3.31832003465372</v>
+      </c>
+      <c r="O49" t="n">
+        <v>60</v>
+      </c>
+      <c r="P49" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>46</v>
+      </c>
+      <c r="R49" t="n">
+        <v>74</v>
+      </c>
+      <c r="S49" t="n">
+        <v>65</v>
+      </c>
+      <c r="T49" t="n">
+        <v>25</v>
+      </c>
+      <c r="U49" t="n">
+        <v>75</v>
+      </c>
+      <c r="V49" t="n">
+        <v>45.73170731707317</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B50" t="n">
+        <v>-0.4425669346467171</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.4368750373498739</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.1158862164200929</v>
+      </c>
+      <c r="E50" t="n">
+        <v>19.93651934481076</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1215641423464071</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>(164, 56)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1.278258385015145</v>
+      </c>
+      <c r="O50" t="n">
+        <v>60</v>
+      </c>
+      <c r="P50" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>46</v>
+      </c>
+      <c r="R50" t="n">
+        <v>81</v>
+      </c>
+      <c r="S50" t="n">
+        <v>67</v>
+      </c>
+      <c r="T50" t="n">
+        <v>16</v>
+      </c>
+      <c r="U50" t="n">
+        <v>72</v>
+      </c>
+      <c r="V50" t="n">
+        <v>43.90243902439025</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B51" t="n">
+        <v>-1.243608889519273</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.1612460207231302</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.2362146249269394</v>
+      </c>
+      <c r="E51" t="n">
+        <v>18.78900309551608</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1145670920458298</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>(164, 58)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1.710511127853188</v>
+      </c>
+      <c r="O51" t="n">
+        <v>60</v>
+      </c>
+      <c r="P51" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>46</v>
+      </c>
+      <c r="R51" t="n">
+        <v>87</v>
+      </c>
+      <c r="S51" t="n">
+        <v>63</v>
+      </c>
+      <c r="T51" t="n">
+        <v>14</v>
+      </c>
+      <c r="U51" t="n">
+        <v>67</v>
+      </c>
+      <c r="V51" t="n">
+        <v>40.85365853658536</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.5561472294298224</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.1035978588354408</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.09077297839726156</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17.33050636288858</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.105673819285906</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>(164, 22)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>2.020038642437223</v>
+      </c>
+      <c r="O52" t="n">
+        <v>60</v>
+      </c>
+      <c r="P52" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>46</v>
+      </c>
+      <c r="R52" t="n">
+        <v>62</v>
+      </c>
+      <c r="S52" t="n">
+        <v>78</v>
+      </c>
+      <c r="T52" t="n">
+        <v>24</v>
+      </c>
+      <c r="U52" t="n">
+        <v>72</v>
+      </c>
+      <c r="V52" t="n">
+        <v>43.90243902439025</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>403</v>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.405771588518279</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.006916272101322107</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3737724590542678</v>
+      </c>
+      <c r="E53" t="n">
+        <v>15.96291716477452</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.09733486076082026</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>(164, 20)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>13.07331280997661</v>
+      </c>
+      <c r="O53" t="n">
+        <v>60</v>
+      </c>
+      <c r="P53" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>46</v>
+      </c>
+      <c r="R53" t="n">
+        <v>72</v>
+      </c>
+      <c r="S53" t="n">
+        <v>70</v>
+      </c>
+      <c r="T53" t="n">
+        <v>22</v>
+      </c>
+      <c r="U53" t="n">
+        <v>70</v>
+      </c>
+      <c r="V53" t="n">
+        <v>42.68292682926829</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B54" t="n">
+        <v>-0.7758626451074774</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.1182133642912416</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.009053932276387778</v>
+      </c>
+      <c r="E54" t="n">
+        <v>12.69391904540814</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.07740194539883011</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>(164, 53)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1.654764762536792</v>
+      </c>
+      <c r="O54" t="n">
+        <v>60</v>
+      </c>
+      <c r="P54" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>46</v>
+      </c>
+      <c r="R54" t="n">
+        <v>85</v>
+      </c>
+      <c r="S54" t="n">
+        <v>69</v>
+      </c>
+      <c r="T54" t="n">
+        <v>10</v>
+      </c>
+      <c r="U54" t="n">
+        <v>71</v>
+      </c>
+      <c r="V54" t="n">
+        <v>43.29268292682926</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>349</v>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.9903126303378055</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.3078951572810193</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.1172225782950266</v>
+      </c>
+      <c r="E55" t="n">
+        <v>11.5049744484794</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.07015228322243537</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>(164, 46)</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1.227844711303486</v>
+      </c>
+      <c r="O55" t="n">
+        <v>60</v>
+      </c>
+      <c r="P55" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>46</v>
+      </c>
+      <c r="R55" t="n">
+        <v>70</v>
+      </c>
+      <c r="S55" t="n">
+        <v>47</v>
+      </c>
+      <c r="T55" t="n">
+        <v>47</v>
+      </c>
+      <c r="U55" t="n">
+        <v>69</v>
+      </c>
+      <c r="V55" t="n">
+        <v>42.07317073170731</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B56" t="n">
+        <v>-0.6331866780480209</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.3301951787858859</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.04546149420378318</v>
+      </c>
+      <c r="E56" t="n">
+        <v>10.08204879053021</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.06147590725933054</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>(164, 59)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1.186180511433798</v>
+      </c>
+      <c r="O56" t="n">
+        <v>60</v>
+      </c>
+      <c r="P56" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>46</v>
+      </c>
+      <c r="R56" t="n">
+        <v>68</v>
+      </c>
+      <c r="S56" t="n">
+        <v>77</v>
+      </c>
+      <c r="T56" t="n">
+        <v>19</v>
+      </c>
+      <c r="U56" t="n">
+        <v>74</v>
+      </c>
+      <c r="V56" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>338</v>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.4166751136564736</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.2248018829579642</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.04710889322561115</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9.746934245733442</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.05943252588861855</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>(164, 13)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1.264377349097791</v>
+      </c>
+      <c r="O57" t="n">
+        <v>60</v>
+      </c>
+      <c r="P57" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>46</v>
+      </c>
+      <c r="R57" t="n">
+        <v>71</v>
+      </c>
+      <c r="S57" t="n">
+        <v>80</v>
+      </c>
+      <c r="T57" t="n">
+        <v>13</v>
+      </c>
+      <c r="U57" t="n">
+        <v>72</v>
+      </c>
+      <c r="V57" t="n">
+        <v>43.90243902439025</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B58" t="n">
+        <v>-0.9653765064458946</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.3682009005837906</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.03528075676553887</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8.443454767324312</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.05148448028856287</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>(164, 25)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1.139827143841672</v>
+      </c>
+      <c r="O58" t="n">
+        <v>60</v>
+      </c>
+      <c r="P58" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>46</v>
+      </c>
+      <c r="R58" t="n">
+        <v>75</v>
+      </c>
+      <c r="S58" t="n">
+        <v>77</v>
+      </c>
+      <c r="T58" t="n">
+        <v>12</v>
+      </c>
+      <c r="U58" t="n">
+        <v>70</v>
+      </c>
+      <c r="V58" t="n">
+        <v>42.68292682926829</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>356</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-0.1334794483872076</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.01539202612787221</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.030376547191606</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7.741970775736235</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.04720713887644046</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>(164, 52)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2.06698666467027</v>
+      </c>
+      <c r="O59" t="n">
+        <v>60</v>
+      </c>
+      <c r="P59" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>46</v>
+      </c>
+      <c r="R59" t="n">
+        <v>78</v>
+      </c>
+      <c r="S59" t="n">
+        <v>66</v>
+      </c>
+      <c r="T59" t="n">
+        <v>20</v>
+      </c>
+      <c r="U59" t="n">
+        <v>68</v>
+      </c>
+      <c r="V59" t="n">
+        <v>41.46341463414634</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B60" t="n">
+        <v>-1.076375845408949</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.1092389015885219</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.1122752498273479</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7.628725466904456</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.04651661870063693</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>(164, 51)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1.425824665244754</v>
+      </c>
+      <c r="O60" t="n">
+        <v>60</v>
+      </c>
+      <c r="P60" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>46</v>
+      </c>
+      <c r="R60" t="n">
+        <v>66</v>
+      </c>
+      <c r="S60" t="n">
+        <v>75</v>
+      </c>
+      <c r="T60" t="n">
+        <v>23</v>
+      </c>
+      <c r="U60" t="n">
+        <v>66</v>
+      </c>
+      <c r="V60" t="n">
+        <v>40.2439024390244</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B61" t="n">
+        <v>-0.5132171464903902</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.1331306902440414</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.02517308784383725</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6.742369823056364</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.04111201111619735</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>(164, 40)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1.308809419081619</v>
+      </c>
+      <c r="O61" t="n">
+        <v>60</v>
+      </c>
+      <c r="P61" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>46</v>
+      </c>
+      <c r="R61" t="n">
+        <v>72</v>
+      </c>
+      <c r="S61" t="n">
+        <v>63</v>
+      </c>
+      <c r="T61" t="n">
+        <v>29</v>
+      </c>
+      <c r="U61" t="n">
+        <v>75</v>
+      </c>
+      <c r="V61" t="n">
+        <v>45.73170731707317</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>342</v>
+      </c>
+      <c r="B62" t="n">
+        <v>-0.4926726584283918</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.009564310268742134</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.08861678450758859</v>
+      </c>
+      <c r="E62" t="n">
+        <v>6.677568409124973</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.04071688054344496</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>(164, 22)</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>5.257168514964948</v>
+      </c>
+      <c r="O62" t="n">
+        <v>60</v>
+      </c>
+      <c r="P62" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>46</v>
+      </c>
+      <c r="R62" t="n">
+        <v>82</v>
+      </c>
+      <c r="S62" t="n">
+        <v>56</v>
+      </c>
+      <c r="T62" t="n">
+        <v>26</v>
+      </c>
+      <c r="U62" t="n">
+        <v>72</v>
+      </c>
+      <c r="V62" t="n">
+        <v>43.90243902439025</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B63" t="n">
         <v>-0.8907288732081902</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C63" t="n">
         <v>-0.3582422798826891</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D63" t="n">
         <v>0.2147455038058414</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E63" t="n">
         <v>5.231285229762435</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F63" t="n">
         <v>0.03189808066928314</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G63" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>(164, 30)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>XGBClassifier</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="N63" t="n">
         <v>1.089040524975803</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
+      <c r="O63" t="n">
+        <v>60</v>
+      </c>
+      <c r="P63" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>46</v>
+      </c>
+      <c r="R63" t="n">
         <v>83</v>
       </c>
-      <c r="S7" t="n">
-        <v>60</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="S63" t="n">
+        <v>60</v>
+      </c>
+      <c r="T63" t="n">
         <v>21</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U63" t="n">
         <v>72</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V63" t="n">
         <v>43.90243902439025</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B64" t="n">
+        <v>-0.07014857349597037</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.0168130122842031</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.03807820395306644</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4.845821101035952</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.02954768964046312</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>(164, 27)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0.7574298490357418</v>
+      </c>
+      <c r="O64" t="n">
+        <v>60</v>
+      </c>
+      <c r="P64" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>46</v>
+      </c>
+      <c r="R64" t="n">
+        <v>73</v>
+      </c>
+      <c r="S64" t="n">
+        <v>75</v>
+      </c>
+      <c r="T64" t="n">
+        <v>16</v>
+      </c>
+      <c r="U64" t="n">
+        <v>74</v>
+      </c>
+      <c r="V64" t="n">
+        <v>45.1219512195122</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.1012540562247923</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.01695092044864154</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.03201975492241568</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4.638733928505729</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.02828496297869347</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>(164, 16)</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0.6686387659237851</v>
+      </c>
+      <c r="O65" t="n">
+        <v>60</v>
+      </c>
+      <c r="P65" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>46</v>
+      </c>
+      <c r="R65" t="n">
+        <v>80</v>
+      </c>
+      <c r="S65" t="n">
+        <v>60</v>
+      </c>
+      <c r="T65" t="n">
+        <v>24</v>
+      </c>
+      <c r="U65" t="n">
+        <v>73</v>
+      </c>
+      <c r="V65" t="n">
+        <v>44.51219512195122</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B66" t="n">
+        <v>-0.09132154938169236</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.006913329111136904</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.02476282169742925</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3.981042102070575</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.02427464696384497</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>(164, 44)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2.511281840284467</v>
+      </c>
+      <c r="O66" t="n">
+        <v>60</v>
+      </c>
+      <c r="P66" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>46</v>
+      </c>
+      <c r="R66" t="n">
+        <v>70</v>
+      </c>
+      <c r="S66" t="n">
+        <v>81</v>
+      </c>
+      <c r="T66" t="n">
+        <v>13</v>
+      </c>
+      <c r="U66" t="n">
+        <v>71</v>
+      </c>
+      <c r="V66" t="n">
+        <v>43.29268292682926</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p4_modeling/2024-10-12/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-12/df_best_model.xlsx
@@ -546,13 +546,13 @@
         <v>38.49424690732052</v>
       </c>
       <c r="D2" t="n">
-        <v>66.38692321761452</v>
+        <v>66.38692321761455</v>
       </c>
       <c r="E2" t="n">
-        <v>8926.047053286706</v>
+        <v>8631.951133411683</v>
       </c>
       <c r="F2" t="n">
-        <v>54.42711617857747</v>
+        <v>50.77618313771578</v>
       </c>
       <c r="G2" t="n">
         <v>-0.25</v>
@@ -577,7 +577,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(164, 65)</t>
+          <t>(170, 65)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -586,31 +586,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.4139026101645065</v>
+        <v>0.3190590079594356</v>
       </c>
       <c r="O2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q2" t="n">
         <v>46</v>
       </c>
       <c r="R2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="S2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="T2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="V2" t="n">
-        <v>46.34146341463415</v>
+        <v>46.47058823529412</v>
       </c>
     </row>
     <row r="3">
@@ -627,10 +627,10 @@
         <v>7.435290830037892</v>
       </c>
       <c r="E3" t="n">
-        <v>1677.369356037947</v>
+        <v>1760.498427257601</v>
       </c>
       <c r="F3" t="n">
-        <v>10.22786192706065</v>
+        <v>10.3558731015153</v>
       </c>
       <c r="G3" t="n">
         <v>-0.35</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(164, 77)</t>
+          <t>(170, 77)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -664,31 +664,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.817869854748674</v>
+        <v>1.853138108479431</v>
       </c>
       <c r="O3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q3" t="n">
         <v>46</v>
       </c>
       <c r="R3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="S3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V3" t="n">
-        <v>48.17073170731707</v>
+        <v>48.23529411764706</v>
       </c>
     </row>
     <row r="4">
@@ -705,10 +705,10 @@
         <v>2.720145318314576</v>
       </c>
       <c r="E4" t="n">
-        <v>498.3527358038604</v>
+        <v>762.9598942567898</v>
       </c>
       <c r="F4" t="n">
-        <v>3.038736193925978</v>
+        <v>4.487999377981116</v>
       </c>
       <c r="G4" t="n">
         <v>-0.25</v>
@@ -733,7 +733,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(164, 65)</t>
+          <t>(170, 65)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,31 +742,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>77.82788633681471</v>
+        <v>115.4232372505214</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
         <v>46</v>
       </c>
       <c r="R4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="S4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="T4" t="n">
         <v>23</v>
       </c>
       <c r="U4" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="V4" t="n">
-        <v>45.1219512195122</v>
+        <v>45.88235294117647</v>
       </c>
     </row>
     <row r="5">
@@ -783,10 +783,10 @@
         <v>3.329034859606559</v>
       </c>
       <c r="E5" t="n">
-        <v>423.2870124604217</v>
+        <v>683.579904380509</v>
       </c>
       <c r="F5" t="n">
-        <v>2.581018368661108</v>
+        <v>4.021058261061818</v>
       </c>
       <c r="G5" t="n">
         <v>-0.25</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(164, 65)</t>
+          <t>(170, 65)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -820,31 +820,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.2263976449957225</v>
+        <v>0.9106475341804555</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q5" t="n">
         <v>46</v>
       </c>
       <c r="R5" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="S5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="V5" t="n">
-        <v>45.73170731707317</v>
+        <v>46.47058823529412</v>
       </c>
     </row>
     <row r="6">
@@ -858,13 +858,13 @@
         <v>1.270713017851595</v>
       </c>
       <c r="D6" t="n">
-        <v>2.003201850243622</v>
+        <v>2.003201850243618</v>
       </c>
       <c r="E6" t="n">
-        <v>409.4509320684475</v>
+        <v>654.3566204991439</v>
       </c>
       <c r="F6" t="n">
-        <v>2.496652024807607</v>
+        <v>3.849156591171435</v>
       </c>
       <c r="G6" t="n">
         <v>-0.25</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(164, 67)</t>
+          <t>(170, 67)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -898,51 +898,51 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.9647646555386021</v>
+        <v>2.029131312181908</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q6" t="n">
         <v>46</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S6" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T6" t="n">
         <v>20</v>
       </c>
       <c r="U6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="V6" t="n">
-        <v>44.51219512195122</v>
+        <v>45.29411764705883</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>299</v>
+        <v>25</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.393589147382974</v>
+        <v>-1.29383869787502</v>
       </c>
       <c r="C7" t="n">
-        <v>1.909588996726958</v>
+        <v>0.5779623475030555</v>
       </c>
       <c r="D7" t="n">
-        <v>3.065686008597786</v>
+        <v>1.842682869246092</v>
       </c>
       <c r="E7" t="n">
-        <v>344.7092103495053</v>
+        <v>334.6263292103833</v>
       </c>
       <c r="F7" t="n">
-        <v>2.101885428960399</v>
+        <v>1.968390171825784</v>
       </c>
       <c r="G7" t="n">
         <v>-0.25</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(164, 8)</t>
+          <t>(170, 31)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -976,51 +976,51 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.1007004295495195</v>
+        <v>2.405741187691085</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q7" t="n">
         <v>46</v>
       </c>
       <c r="R7" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="S7" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="U7" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="V7" t="n">
-        <v>45.1219512195122</v>
+        <v>45.88235294117647</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.29383869787502</v>
+        <v>-1.270711100532256</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5779623475030555</v>
+        <v>0.1992282837143054</v>
       </c>
       <c r="D8" t="n">
-        <v>1.842682869246092</v>
+        <v>2.053024831311012</v>
       </c>
       <c r="E8" t="n">
-        <v>331.0515237994687</v>
+        <v>236.9797700308348</v>
       </c>
       <c r="F8" t="n">
-        <v>2.018606852435785</v>
+        <v>1.393998647240205</v>
       </c>
       <c r="G8" t="n">
         <v>-0.25</v>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(164, 31)</t>
+          <t>(170, 42)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1054,51 +1054,51 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.492626917924118</v>
+        <v>5.996991698423742</v>
       </c>
       <c r="O8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P8" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q8" t="n">
         <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="S8" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="T8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="U8" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="V8" t="n">
-        <v>45.73170731707317</v>
+        <v>46.47058823529412</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>124</v>
+        <v>359</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.270711100532256</v>
+        <v>-1.281603424354408</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1992282837143054</v>
+        <v>0.08088815800616288</v>
       </c>
       <c r="D9" t="n">
-        <v>2.053024831311012</v>
+        <v>1.437106167280731</v>
       </c>
       <c r="E9" t="n">
-        <v>228.3952213169126</v>
+        <v>194.7226639965467</v>
       </c>
       <c r="F9" t="n">
-        <v>1.39265378851776</v>
+        <v>1.145427435273804</v>
       </c>
       <c r="G9" t="n">
         <v>-0.25</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(164, 42)</t>
+          <t>(170, 39)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1132,54 +1132,54 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.990241358073606</v>
+        <v>13.1606319578514</v>
       </c>
       <c r="O9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q9" t="n">
         <v>46</v>
       </c>
       <c r="R9" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="S9" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="T9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="U9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="V9" t="n">
-        <v>46.34146341463415</v>
+        <v>46.47058823529412</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>359</v>
+        <v>42</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.281603424354408</v>
+        <v>-0.08541661905859201</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08088815800616288</v>
+        <v>0.6368493526320456</v>
       </c>
       <c r="D10" t="n">
-        <v>1.437106167280731</v>
+        <v>0.5886110665875758</v>
       </c>
       <c r="E10" t="n">
-        <v>189.3215640517438</v>
+        <v>155.159924643413</v>
       </c>
       <c r="F10" t="n">
-        <v>1.154399780803316</v>
+        <v>0.9127054390788999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1201,63 +1201,63 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(164, 39)</t>
+          <t>(170, 51)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>13.27155481418382</v>
+        <v>0.4331575203880855</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P10" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="n">
         <v>46</v>
       </c>
       <c r="R10" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="S10" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="T10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="U10" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="V10" t="n">
-        <v>46.34146341463415</v>
+        <v>48.8235294117647</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>238</v>
+        <v>460</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.863279229568991</v>
+        <v>0.6160002910800761</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.6045860133527742</v>
+        <v>-0.2590851495874979</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7938181292726201</v>
+        <v>0.4015444161954616</v>
       </c>
       <c r="E11" t="n">
-        <v>169.9763727180111</v>
+        <v>139.2419893795158</v>
       </c>
       <c r="F11" t="n">
-        <v>1.036441297061043</v>
+        <v>0.8190705257618576</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(164, 50)</t>
+          <t>(170, 30)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1288,54 +1288,54 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.71429916367629</v>
+        <v>4.161395113019561</v>
       </c>
       <c r="O11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P11" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q11" t="n">
         <v>46</v>
       </c>
       <c r="R11" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="S11" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="T11" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="U11" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="V11" t="n">
-        <v>45.73170731707317</v>
+        <v>48.23529411764706</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.9159825864001954</v>
+        <v>-0.1025706956479561</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5754312203429623</v>
+        <v>0.08963819641877152</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6954712754722374</v>
+        <v>0.8355662296590918</v>
       </c>
       <c r="E12" t="n">
-        <v>125.6449291941915</v>
+        <v>122.5966196748957</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7661276170377531</v>
+        <v>0.7211565863229159</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1357,60 +1357,60 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>(164, 29)</t>
+          <t>(170, 77)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.3313973763556554</v>
+        <v>7.04519295495213</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q12" t="n">
         <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="S12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="V12" t="n">
-        <v>43.90243902439025</v>
+        <v>45.29411764705883</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>137</v>
+        <v>231</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.1025706956479567</v>
+        <v>-0.7308108907700971</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08963819641877152</v>
+        <v>0.2101749345543405</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8355662296590918</v>
+        <v>0.483898655699301</v>
       </c>
       <c r="E13" t="n">
-        <v>116.903222141034</v>
+        <v>117.6580112198883</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7128245252502073</v>
+        <v>0.6921059483522841</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(164, 77)</t>
+          <t>(170, 22)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1444,51 +1444,51 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.952240827336992</v>
+        <v>2.292999471225437</v>
       </c>
       <c r="O13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P13" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q13" t="n">
         <v>46</v>
       </c>
       <c r="R13" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="S13" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="T13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U13" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="V13" t="n">
-        <v>45.1219512195122</v>
+        <v>46.47058823529412</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>231</v>
+        <v>407</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.7308108907700976</v>
+        <v>-1.23038361130531</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2101749345543382</v>
+        <v>-0.1951992963691856</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4838986556992986</v>
+        <v>0.1187709119949317</v>
       </c>
       <c r="E14" t="n">
-        <v>115.0545731115202</v>
+        <v>115.8712758120188</v>
       </c>
       <c r="F14" t="n">
-        <v>0.701552275070245</v>
+        <v>0.6815957400706989</v>
       </c>
       <c r="G14" t="n">
         <v>-0.5</v>
@@ -1513,60 +1513,60 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>(164, 22)</t>
+          <t>(170, 67)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.337944539189886</v>
+        <v>4.491794042031682</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q14" t="n">
         <v>46</v>
       </c>
       <c r="R14" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="S14" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="T14" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="U14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V14" t="n">
-        <v>46.34146341463415</v>
+        <v>45.29411764705883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.08541661905859144</v>
+        <v>0.7872862624629369</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6368493526320452</v>
+        <v>-0.00830850585574467</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5886110665875751</v>
+        <v>0.7738854644366558</v>
       </c>
       <c r="E15" t="n">
-        <v>108.0236596256396</v>
+        <v>105.9687267322284</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6586808513758512</v>
+        <v>0.6233454513660494</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5</v>
@@ -1591,60 +1591,60 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>(164, 51)</t>
+          <t>(170, 47)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.03428047567855444</v>
+        <v>76.02497587277448</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q15" t="n">
         <v>46</v>
       </c>
       <c r="R15" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="S15" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="T15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="U15" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="V15" t="n">
-        <v>48.17073170731707</v>
+        <v>45.29411764705883</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7872862624629369</v>
+        <v>0.5387685651725178</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.00830850585574467</v>
+        <v>-0.2575614088561794</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7738854644366558</v>
+        <v>0.6152593578413085</v>
       </c>
       <c r="E16" t="n">
-        <v>107.3044152880446</v>
+        <v>97.03877536401541</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6542952151710039</v>
+        <v>0.5708163256706789</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>(164, 47)</t>
+          <t>(170, 17)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1678,54 +1678,54 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>79.75004561964784</v>
+        <v>3.216233900123675</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P16" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q16" t="n">
         <v>46</v>
       </c>
       <c r="R16" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S16" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="T16" t="n">
         <v>24</v>
       </c>
       <c r="U16" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V16" t="n">
-        <v>45.1219512195122</v>
+        <v>44.70588235294118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.202522073267674</v>
+        <v>-0.8084740289345299</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3114694487797945</v>
+        <v>0.2472274703035632</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3659698589989949</v>
+        <v>0.1173185206593994</v>
       </c>
       <c r="E17" t="n">
-        <v>95.44078115492562</v>
+        <v>88.23610227101898</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5819559826519854</v>
+        <v>0.5190358957118764</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>(164, 23)</t>
+          <t>(170, 43)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1756,54 +1756,54 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.8684207550109417</v>
+        <v>1.099426471801729</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P17" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
       </c>
       <c r="R17" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="S17" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U17" t="n">
         <v>72</v>
       </c>
       <c r="V17" t="n">
-        <v>43.90243902439025</v>
+        <v>42.35294117647059</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>391</v>
+        <v>210</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.8084740289345299</v>
+        <v>-0.7076435728528068</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2472274703035632</v>
+        <v>-0.3595907076545838</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1173185206593994</v>
+        <v>0.3817845703131216</v>
       </c>
       <c r="E18" t="n">
-        <v>85.55547355762971</v>
+        <v>80.72206880382461</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5216797168148153</v>
+        <v>0.4748356988460271</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1825,63 +1825,63 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>(164, 43)</t>
+          <t>(170, 47)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.110120352622063</v>
+        <v>2.320489347300224</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P18" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q18" t="n">
         <v>46</v>
       </c>
       <c r="R18" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="S18" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="T18" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="U18" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="V18" t="n">
-        <v>42.07317073170731</v>
+        <v>48.23529411764706</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5387685651725178</v>
+        <v>-0.4183903751825491</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2575614088561794</v>
+        <v>0.2323702533209567</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6152593578413085</v>
+        <v>0.5397711384304422</v>
       </c>
       <c r="E19" t="n">
-        <v>85.46893504322568</v>
+        <v>79.28182905114537</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5211520429464981</v>
+        <v>0.4663637003008551</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>(164, 17)</t>
+          <t>(170, 25)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1912,51 +1912,51 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.023408884354667</v>
+        <v>1.006985376293839</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P19" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="n">
         <v>46</v>
       </c>
       <c r="R19" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="S19" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="T19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U19" t="n">
         <v>74</v>
       </c>
       <c r="V19" t="n">
-        <v>45.1219512195122</v>
+        <v>43.52941176470588</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.6864414057829122</v>
+        <v>-1.298445540844414</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3902779398667633</v>
+        <v>-0.1426574248687518</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5597692970039736</v>
+        <v>0.5110236516481946</v>
       </c>
       <c r="E20" t="n">
-        <v>78.55616861720677</v>
+        <v>75.60164296220384</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4790010281536998</v>
+        <v>0.4447155468364932</v>
       </c>
       <c r="G20" t="n">
         <v>-0.25</v>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>(164, 49)</t>
+          <t>(170, 47)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1990,54 +1990,54 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.2273330855370037</v>
+        <v>4.117366987702476</v>
       </c>
       <c r="O20" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P20" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q20" t="n">
         <v>46</v>
       </c>
       <c r="R20" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="S20" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="T20" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="U20" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V20" t="n">
-        <v>42.07317073170731</v>
+        <v>42.35294117647059</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>373</v>
+        <v>87</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.6495371033671955</v>
+        <v>-0.419231764767878</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.01258303421742198</v>
+        <v>-0.2087440871096707</v>
       </c>
       <c r="D21" t="n">
-        <v>0.365304195919043</v>
+        <v>0.531386164383318</v>
       </c>
       <c r="E21" t="n">
-        <v>74.92421641985342</v>
+        <v>75.21198553190817</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4568549781698379</v>
+        <v>0.4424234443053422</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>(164, 39)</t>
+          <t>(170, 21)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>37.30721893271928</v>
+        <v>3.11945377917651</v>
       </c>
       <c r="O21" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P21" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q21" t="n">
         <v>46</v>
@@ -2083,39 +2083,39 @@
         <v>72</v>
       </c>
       <c r="S21" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="T21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U21" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V21" t="n">
-        <v>45.73170731707317</v>
+        <v>43.52941176470588</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.4183903751825488</v>
+        <v>-0.7590930908186222</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2323702533209567</v>
+        <v>-0.201545842318864</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5397711384304424</v>
+        <v>0.3256250402432596</v>
       </c>
       <c r="E22" t="n">
-        <v>71.68923038730804</v>
+        <v>74.59662633075496</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4371294535811466</v>
+        <v>0.4388036842985586</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2137,63 +2137,63 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>(164, 25)</t>
+          <t>(170, 58)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.8811764730374951</v>
+        <v>3.177190455778943</v>
       </c>
       <c r="O22" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P22" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q22" t="n">
         <v>46</v>
       </c>
       <c r="R22" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="S22" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="T22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U22" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="V22" t="n">
-        <v>43.29268292682926</v>
+        <v>44.70588235294118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>100</v>
+        <v>373</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.298445540844414</v>
+        <v>-0.6495371033671955</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1426574248687518</v>
+        <v>-0.01258303421742198</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5110236516481954</v>
+        <v>0.365304195919043</v>
       </c>
       <c r="E23" t="n">
-        <v>71.51708348233416</v>
+        <v>74.36211999831716</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4360797773313058</v>
+        <v>0.4374242352842185</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2215,60 +2215,60 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>(164, 47)</t>
+          <t>(170, 39)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.056831971644725</v>
+        <v>35.76301722827534</v>
       </c>
       <c r="O23" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P23" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q23" t="n">
         <v>46</v>
       </c>
       <c r="R23" t="n">
+        <v>76</v>
+      </c>
+      <c r="S23" t="n">
+        <v>82</v>
+      </c>
+      <c r="T23" t="n">
+        <v>12</v>
+      </c>
+      <c r="U23" t="n">
         <v>78</v>
       </c>
-      <c r="S23" t="n">
-        <v>65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>21</v>
-      </c>
-      <c r="U23" t="n">
-        <v>69</v>
-      </c>
       <c r="V23" t="n">
-        <v>42.07317073170731</v>
+        <v>45.88235294117647</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>283</v>
+        <v>50</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.7590930908186222</v>
+        <v>-0.1772591716471172</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.201545842318864</v>
+        <v>-0.08916231945623763</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3256250402432596</v>
+        <v>0.295812302060012</v>
       </c>
       <c r="E24" t="n">
-        <v>68.81743421479914</v>
+        <v>74.33222139317303</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4196185013097508</v>
+        <v>0.4372483611363119</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>(164, 58)</t>
+          <t>(170, 30)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2302,31 +2302,31 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.082000285800368</v>
+        <v>5.903959024427587</v>
       </c>
       <c r="O24" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P24" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q24" t="n">
         <v>46</v>
       </c>
       <c r="R24" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="S24" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U24" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="V24" t="n">
-        <v>44.51219512195122</v>
+        <v>45.29411764705883</v>
       </c>
     </row>
     <row r="25">
@@ -2334,19 +2334,19 @@
         <v>220</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.3018470033094539</v>
+        <v>-0.301847003309455</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0184048499194067</v>
+        <v>-0.01840484991940812</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4886607761800034</v>
+        <v>0.4886607761800017</v>
       </c>
       <c r="E25" t="n">
-        <v>68.35783628181818</v>
+        <v>73.52336649297368</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4168160748891352</v>
+        <v>0.4324903911351393</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>(164, 48)</t>
+          <t>(170, 48)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2380,51 +2380,51 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>23.64707817310861</v>
+        <v>24.49871870886995</v>
       </c>
       <c r="O25" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P25" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q25" t="n">
         <v>46</v>
       </c>
       <c r="R25" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="S25" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T25" t="n">
         <v>11</v>
       </c>
       <c r="U25" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="V25" t="n">
-        <v>43.29268292682926</v>
+        <v>43.52941176470588</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>50</v>
+        <v>445</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.1772591716471172</v>
+        <v>-0.3133139529145339</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.08916231945623763</v>
+        <v>0.1530488437017718</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2958123020600122</v>
+        <v>0.5171421638048482</v>
       </c>
       <c r="E26" t="n">
-        <v>67.64450599438334</v>
+        <v>68.63801868632828</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4124664999657521</v>
+        <v>0.4037530510960487</v>
       </c>
       <c r="G26" t="n">
         <v>-0.5</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>(164, 30)</t>
+          <t>(170, 66)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2458,54 +2458,54 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>5.626018058763012</v>
+        <v>1.638066654608607</v>
       </c>
       <c r="O26" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P26" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>46</v>
+      </c>
+      <c r="R26" t="n">
+        <v>79</v>
+      </c>
+      <c r="S26" t="n">
         <v>58</v>
       </c>
-      <c r="Q26" t="n">
-        <v>46</v>
-      </c>
-      <c r="R26" t="n">
-        <v>76</v>
-      </c>
-      <c r="S26" t="n">
-        <v>77</v>
-      </c>
       <c r="T26" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="U26" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="V26" t="n">
-        <v>45.1219512195122</v>
+        <v>46.47058823529412</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>407</v>
+        <v>120</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.23038361130531</v>
+        <v>-0.3735886662604463</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1951992963691856</v>
+        <v>0.2211429387574934</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1187709119949317</v>
+        <v>0.3835664364271457</v>
       </c>
       <c r="E27" t="n">
-        <v>66.93106740716465</v>
+        <v>68.06341373808215</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4081162646778332</v>
+        <v>0.4003730219887185</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>(164, 67)</t>
+          <t>(170, 22)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2536,51 +2536,51 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.090767089169995</v>
+        <v>0.8104716534845811</v>
       </c>
       <c r="O27" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P27" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q27" t="n">
         <v>46</v>
       </c>
       <c r="R27" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S27" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T27" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="U27" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V27" t="n">
-        <v>44.51219512195122</v>
+        <v>43.52941176470588</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>117</v>
+        <v>415</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.201143692429389</v>
+        <v>-0.3824306631146794</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08932629065833851</v>
+        <v>0.3509124580478499</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5501876732815073</v>
+        <v>0.3558019892225995</v>
       </c>
       <c r="E28" t="n">
-        <v>60.67921570260708</v>
+        <v>64.00027715590744</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3699952176988237</v>
+        <v>0.3764722185641614</v>
       </c>
       <c r="G28" t="n">
         <v>-0.25</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>(164, 44)</t>
+          <t>(170, 43)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2614,51 +2614,51 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.142064054960117</v>
+        <v>0.0728379968568293</v>
       </c>
       <c r="O28" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P28" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q28" t="n">
         <v>46</v>
       </c>
       <c r="R28" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="T28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="U28" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V28" t="n">
-        <v>44.51219512195122</v>
+        <v>43.52941176470588</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>415</v>
+        <v>12</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.3824306631146794</v>
+        <v>-0.627819056574129</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3509124580478499</v>
+        <v>-0.3038149578046913</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3558019892225991</v>
+        <v>0.5295452224404471</v>
       </c>
       <c r="E29" t="n">
-        <v>60.39887618210983</v>
+        <v>60.53133761123775</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3682858303787185</v>
+        <v>0.3560666918308102</v>
       </c>
       <c r="G29" t="n">
         <v>-0.25</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>(164, 43)</t>
+          <t>(170, 37)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2692,54 +2692,54 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.04950913520573728</v>
+        <v>2.171985390066638</v>
       </c>
       <c r="O29" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P29" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q29" t="n">
         <v>46</v>
       </c>
       <c r="R29" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="S29" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="T29" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="U29" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="V29" t="n">
-        <v>43.29268292682926</v>
+        <v>45.88235294117647</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>431</v>
+        <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.758487333493334</v>
+        <v>-0.6889365617839698</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2820740912587257</v>
+        <v>0.2663784624785005</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05688237791939372</v>
+        <v>0.778758895649977</v>
       </c>
       <c r="E30" t="n">
-        <v>58.23946200138621</v>
+        <v>59.61172429118494</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3551186707401598</v>
+        <v>0.3506572017128526</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2761,63 +2761,63 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>(164, 67)</t>
+          <t>(170, 34)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.258955294885398</v>
+        <v>0.3163872125778722</v>
       </c>
       <c r="O30" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P30" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q30" t="n">
         <v>46</v>
       </c>
       <c r="R30" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S30" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="T30" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="U30" t="n">
         <v>74</v>
       </c>
       <c r="V30" t="n">
-        <v>45.1219512195122</v>
+        <v>43.52941176470588</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>36</v>
+        <v>431</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.6889365617839698</v>
+        <v>-0.758487333493334</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2663784624785005</v>
+        <v>-0.2820740912587257</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7787588956499777</v>
+        <v>0.05688237791939372</v>
       </c>
       <c r="E31" t="n">
-        <v>57.78770750570732</v>
+        <v>59.40957451916086</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3523640701567519</v>
+        <v>0.3494680854068286</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2839,63 +2839,63 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>(164, 34)</t>
+          <t>(170, 67)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.3227948944453096</v>
+        <v>2.238923021420947</v>
       </c>
       <c r="O31" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P31" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q31" t="n">
         <v>46</v>
       </c>
       <c r="R31" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="S31" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="T31" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="U31" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V31" t="n">
-        <v>43.29268292682926</v>
+        <v>45.29411764705883</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>12</v>
+        <v>274</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.627819056574129</v>
+        <v>0.1161149784369491</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3038149578046913</v>
+        <v>0.193617586547545</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5295770827090096</v>
+        <v>0.2777094383950248</v>
       </c>
       <c r="E32" t="n">
-        <v>56.5375202930687</v>
+        <v>55.59321767126968</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3447409773967604</v>
+        <v>0.3270189274780569</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2917,63 +2917,63 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>(164, 37)</t>
+          <t>(170, 65)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.134707059480523</v>
+        <v>0.6889939251347593</v>
       </c>
       <c r="O32" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P32" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q32" t="n">
         <v>46</v>
       </c>
       <c r="R32" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="S32" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="T32" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="U32" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="V32" t="n">
-        <v>45.73170731707317</v>
+        <v>48.8235294117647</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>247</v>
+        <v>405</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.9665070146464771</v>
+        <v>-0.913212535025712</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2969809755969115</v>
+        <v>0.2641651603330288</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1945905772476886</v>
+        <v>0.2188344244153798</v>
       </c>
       <c r="E33" t="n">
-        <v>54.16908295296221</v>
+        <v>45.70030780328005</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3302992862985501</v>
+        <v>0.2688253400192944</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>(164, 15)</t>
+          <t>(170, 89)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3004,13 +3004,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.1121900506746975</v>
+        <v>0.01764115934285419</v>
       </c>
       <c r="O33" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P33" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q33" t="n">
         <v>46</v>
@@ -3019,36 +3019,36 @@
         <v>69</v>
       </c>
       <c r="S33" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="T33" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="U33" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="V33" t="n">
-        <v>40.85365853658536</v>
+        <v>45.88235294117647</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>274</v>
+        <v>442</v>
       </c>
       <c r="B34" t="n">
-        <v>0.116191777450309</v>
+        <v>-0.640219164487128</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1937545989322405</v>
+        <v>0.01726989817683844</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2778178409719161</v>
+        <v>0.1713774132216737</v>
       </c>
       <c r="E34" t="n">
-        <v>52.15794631164721</v>
+        <v>45.43512248688808</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3180362579978488</v>
+        <v>0.2672654263934593</v>
       </c>
       <c r="G34" t="n">
         <v>-0.5</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>(164, 65)</t>
+          <t>(170, 12)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3082,51 +3082,51 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.6414384987531158</v>
+        <v>14.47579630503571</v>
       </c>
       <c r="O34" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P34" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q34" t="n">
         <v>46</v>
       </c>
       <c r="R34" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S34" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="T34" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="U34" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="V34" t="n">
-        <v>48.78048780487805</v>
+        <v>44.70588235294118</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>405</v>
+        <v>266</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.9132125350257122</v>
+        <v>-0.7758626451074774</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2641651603330276</v>
+        <v>-0.118213364291242</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2188344244153796</v>
+        <v>-0.009053932276387778</v>
       </c>
       <c r="E35" t="n">
-        <v>47.42561091383718</v>
+        <v>40.48795787271186</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2891805543526657</v>
+        <v>0.2381644580747757</v>
       </c>
       <c r="G35" t="n">
         <v>-0.5</v>
@@ -3151,63 +3151,63 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>(164, 89)</t>
+          <t>(170, 53)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0.09469603784277139</v>
+        <v>3.01469994109981</v>
       </c>
       <c r="O35" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P35" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q35" t="n">
         <v>46</v>
       </c>
       <c r="R35" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="S35" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="T35" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="U35" t="n">
         <v>75</v>
       </c>
       <c r="V35" t="n">
-        <v>45.73170731707317</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.7077620915048203</v>
+        <v>-1.201143692429389</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3596212123102464</v>
+        <v>0.08932629065833851</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3817346293701274</v>
+        <v>0.5501876732815073</v>
       </c>
       <c r="E36" t="n">
-        <v>46.88447072089011</v>
+        <v>39.63237772840984</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2858809190298177</v>
+        <v>0.2331316336965285</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3229,63 +3229,63 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>(164, 47)</t>
+          <t>(170, 44)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.794950100950072</v>
+        <v>1.609888219675736</v>
       </c>
       <c r="O36" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P36" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q36" t="n">
         <v>46</v>
       </c>
       <c r="R36" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="S36" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="T36" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="U36" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="V36" t="n">
-        <v>47.5609756097561</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>87</v>
+        <v>239</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.4192317647678772</v>
+        <v>-0.9653765064458946</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2087440871096699</v>
+        <v>-0.3682009005837906</v>
       </c>
       <c r="D37" t="n">
-        <v>0.531386164383319</v>
+        <v>-0.03528075676553887</v>
       </c>
       <c r="E37" t="n">
-        <v>45.91862683516746</v>
+        <v>36.9186121379754</v>
       </c>
       <c r="F37" t="n">
-        <v>0.279991627043704</v>
+        <v>0.2171683066939729</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>(164, 21)</t>
+          <t>(170, 25)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3316,31 +3316,31 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.34131524835289</v>
+        <v>1.589809276266429</v>
       </c>
       <c r="O37" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P37" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q37" t="n">
         <v>46</v>
       </c>
       <c r="R37" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="S37" t="n">
         <v>80</v>
       </c>
       <c r="T37" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U37" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="V37" t="n">
-        <v>42.68292682926829</v>
+        <v>43.52941176470588</v>
       </c>
     </row>
     <row r="38">
@@ -3357,10 +3357,10 @@
         <v>0.3670367141999942</v>
       </c>
       <c r="E38" t="n">
-        <v>45.15764492009609</v>
+        <v>36.124655834387</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2753514934152201</v>
+        <v>0.2124979754963941</v>
       </c>
       <c r="G38" t="n">
         <v>-0.35</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>(164, 29)</t>
+          <t>(170, 29)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3394,54 +3394,54 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.400704878037115</v>
+        <v>0.8527044107145066</v>
       </c>
       <c r="O38" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P38" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q38" t="n">
         <v>46</v>
       </c>
       <c r="R38" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S38" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="T38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U38" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="V38" t="n">
-        <v>43.29268292682926</v>
+        <v>42.94117647058823</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>223</v>
+        <v>5</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.4251678065433589</v>
+        <v>-0.2707332259722691</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2366028533725871</v>
+        <v>-0.2232582881700093</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2458276139207142</v>
+        <v>0.3948171343930217</v>
       </c>
       <c r="E39" t="n">
-        <v>43.55352075366494</v>
+        <v>34.09796106318231</v>
       </c>
       <c r="F39" t="n">
-        <v>0.265570248497957</v>
+        <v>0.2005762415481313</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>(164, 16)</t>
+          <t>(170, 17)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3472,51 +3472,51 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.1224304555607105</v>
+        <v>1.898404458764793</v>
       </c>
       <c r="O39" t="n">
+        <v>63</v>
+      </c>
+      <c r="P39" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>46</v>
+      </c>
+      <c r="R39" t="n">
         <v>60</v>
       </c>
-      <c r="P39" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>46</v>
-      </c>
-      <c r="R39" t="n">
-        <v>69</v>
-      </c>
       <c r="S39" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="T39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U39" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V39" t="n">
-        <v>40.85365853658536</v>
+        <v>41.76470588235294</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.2707332259722691</v>
+        <v>-1.214087270241895</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2232582881700093</v>
+        <v>-0.06527952905788936</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3948171343930221</v>
+        <v>0.4317663856781094</v>
       </c>
       <c r="E40" t="n">
-        <v>40.49978963121458</v>
+        <v>33.92670728801784</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2469499367756987</v>
+        <v>0.1995688664001049</v>
       </c>
       <c r="G40" t="n">
         <v>-0.5</v>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>(164, 17)</t>
+          <t>(170, 14)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3550,51 +3550,51 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.106117666671566</v>
+        <v>4.057143169999417</v>
       </c>
       <c r="O40" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P40" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q40" t="n">
         <v>46</v>
       </c>
       <c r="R40" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="S40" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="T40" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="U40" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V40" t="n">
-        <v>42.07317073170731</v>
+        <v>41.17647058823529</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>120</v>
+        <v>389</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.3735886662604463</v>
+        <v>-0.420108664046501</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2211429387574934</v>
+        <v>0.009141992194604286</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3835664364271457</v>
+        <v>-0.1152580840603443</v>
       </c>
       <c r="E41" t="n">
-        <v>38.76953839840019</v>
+        <v>30.83164602529502</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2363996243804889</v>
+        <v>0.181362623678206</v>
       </c>
       <c r="G41" t="n">
         <v>-0.25</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>(164, 22)</t>
+          <t>(170, 57)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3628,54 +3628,54 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0.06899015500434375</v>
+        <v>18.83841375244757</v>
       </c>
       <c r="O41" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P41" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q41" t="n">
         <v>46</v>
       </c>
       <c r="R41" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="S41" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="T41" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="U41" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="V41" t="n">
-        <v>42.68292682926829</v>
+        <v>42.35294117647059</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.214087270241895</v>
+        <v>-0.8285933157912798</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.06527952905788922</v>
+        <v>-0.1033647087916408</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4317663856781094</v>
+        <v>0.2955218143331052</v>
       </c>
       <c r="E42" t="n">
-        <v>35.95596156410394</v>
+        <v>29.75681824969047</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2192436680738045</v>
+        <v>0.1750401073511204</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>(164, 14)</t>
+          <t>(170, 15)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3706,54 +3706,54 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>4.358536301317087</v>
+        <v>2.693422343054829</v>
       </c>
       <c r="O42" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P42" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q42" t="n">
         <v>46</v>
       </c>
       <c r="R42" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="S42" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="T42" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="U42" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="V42" t="n">
-        <v>40.85365853658536</v>
+        <v>42.94117647058823</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>151</v>
+        <v>280</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.015718323821463</v>
+        <v>-0.846426191819909</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.2801829888464317</v>
+        <v>0.1186233528622965</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1307557621807462</v>
+        <v>0.1752029455036724</v>
       </c>
       <c r="E43" t="n">
-        <v>34.30186506401921</v>
+        <v>28.84264191549385</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2091577138049952</v>
+        <v>0.169662599502905</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>(164, 8)</t>
+          <t>(170, 17)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.74650397108739</v>
+        <v>0.4302630587406953</v>
       </c>
       <c r="O43" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P43" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q43" t="n">
         <v>46</v>
@@ -3799,39 +3799,39 @@
         <v>72</v>
       </c>
       <c r="S43" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="T43" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="U43" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="V43" t="n">
-        <v>42.68292682926829</v>
+        <v>42.35294117647059</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>407</v>
+        <v>92</v>
       </c>
       <c r="B44" t="n">
-        <v>0.00737776448490763</v>
+        <v>-0.9261812924335178</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.2337974436379267</v>
+        <v>-0.06527727279216634</v>
       </c>
       <c r="D44" t="n">
-        <v>0.07696117327230088</v>
+        <v>0.05791706187807686</v>
       </c>
       <c r="E44" t="n">
-        <v>29.01492380239969</v>
+        <v>28.25420727688811</v>
       </c>
       <c r="F44" t="n">
-        <v>0.176920267087803</v>
+        <v>0.1662012192758124</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3853,63 +3853,63 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>(164, 67)</t>
+          <t>(170, 72)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.756724557526783</v>
+        <v>3.546080927813478</v>
       </c>
       <c r="O44" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P44" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q44" t="n">
         <v>46</v>
       </c>
       <c r="R44" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="S44" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="T44" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="U44" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="V44" t="n">
-        <v>45.1219512195122</v>
+        <v>42.35294117647059</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.8465305504779401</v>
+        <v>-0.7703581834752598</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1186060181914459</v>
+        <v>0.03225979211743109</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1751898995283771</v>
+        <v>0.0828623119931539</v>
       </c>
       <c r="E45" t="n">
-        <v>28.77418107980824</v>
+        <v>27.57312483638435</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1754523236573673</v>
+        <v>0.1621948519787315</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3931,63 +3931,63 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>(164, 17)</t>
+          <t>(170, 53)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.4792868551928276</v>
+        <v>4.027771145837358</v>
       </c>
       <c r="O45" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P45" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q45" t="n">
         <v>46</v>
       </c>
       <c r="R45" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="S45" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="T45" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="U45" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="V45" t="n">
-        <v>42.07317073170731</v>
+        <v>45.88235294117647</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.9261812924335178</v>
+        <v>-0.8907288732081902</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.06527727279216634</v>
+        <v>-0.3582422798826891</v>
       </c>
       <c r="D46" t="n">
-        <v>0.05791706187807686</v>
+        <v>0.2147455038058414</v>
       </c>
       <c r="E46" t="n">
-        <v>27.01826435410063</v>
+        <v>25.79375090033106</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1647455143542721</v>
+        <v>0.1517279464725357</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>(164, 72)</t>
+          <t>(170, 30)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4018,54 +4018,54 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.52378059479903</v>
+        <v>1.423534448592223</v>
       </c>
       <c r="O46" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P46" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q46" t="n">
         <v>46</v>
       </c>
       <c r="R46" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="S46" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="T46" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U46" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="V46" t="n">
-        <v>42.07317073170731</v>
+        <v>44.70588235294118</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.8285933157912795</v>
+        <v>-0.4425669346467171</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1033647087916408</v>
+        <v>-0.4368750373498739</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2955218143331052</v>
+        <v>-0.115886216420093</v>
       </c>
       <c r="E47" t="n">
-        <v>26.74556389907136</v>
+        <v>23.91455583980662</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1630827067016546</v>
+        <v>0.1406738578812154</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4087,60 +4087,60 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(164, 15)</t>
+          <t>(170, 56)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.577740687398359</v>
+        <v>1.322000219409552</v>
       </c>
       <c r="O47" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P47" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q47" t="n">
         <v>46</v>
       </c>
       <c r="R47" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="S47" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="T47" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U47" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="V47" t="n">
-        <v>42.68292682926829</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.068636691651434</v>
+        <v>-1.243608889519273</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1200971810313662</v>
+        <v>-0.1612460207231315</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1888853365347014</v>
+        <v>0.2362146249269385</v>
       </c>
       <c r="E48" t="n">
-        <v>22.93456811659929</v>
+        <v>21.97423030624479</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1398449275402396</v>
+        <v>0.1292601782720282</v>
       </c>
       <c r="G48" t="n">
         <v>-0.25</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>(164, 33)</t>
+          <t>(170, 58)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4174,51 +4174,51 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.1644313908060492</v>
+        <v>1.801633291118391</v>
       </c>
       <c r="O48" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P48" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q48" t="n">
         <v>46</v>
       </c>
       <c r="R48" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="S48" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="T48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U48" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V48" t="n">
-        <v>42.07317073170731</v>
+        <v>41.17647058823529</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>265</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.7703581834752598</v>
+        <v>-0.5561472294298224</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03225979211743109</v>
+        <v>-0.1035978588354408</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0828623119931539</v>
+        <v>0.09077297839726156</v>
       </c>
       <c r="E49" t="n">
-        <v>22.84652948477256</v>
+        <v>20.7819349813681</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1393081066144668</v>
+        <v>0.1222466763609888</v>
       </c>
       <c r="G49" t="n">
         <v>-0.5</v>
@@ -4243,31 +4243,31 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>(164, 53)</t>
+          <t>(170, 22)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.31832003465372</v>
+        <v>2.180011611583311</v>
       </c>
       <c r="O49" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P49" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q49" t="n">
         <v>46</v>
       </c>
       <c r="R49" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="S49" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="T49" t="n">
         <v>25</v>
@@ -4276,27 +4276,27 @@
         <v>75</v>
       </c>
       <c r="V49" t="n">
-        <v>45.73170731707317</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.4425669346467171</v>
+        <v>-0.8886531988605186</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4368750373498739</v>
+        <v>-0.173656114559017</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1158862164200929</v>
+        <v>-0.03486900191492822</v>
       </c>
       <c r="E50" t="n">
-        <v>19.93651934481076</v>
+        <v>18.43220952690363</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1215641423464071</v>
+        <v>0.1084247619229625</v>
       </c>
       <c r="G50" t="n">
         <v>-0.5</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>(164, 56)</t>
+          <t>(170, 44)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4330,51 +4330,51 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.278258385015145</v>
+        <v>1.624364780925203</v>
       </c>
       <c r="O50" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P50" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q50" t="n">
         <v>46</v>
       </c>
       <c r="R50" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="S50" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="T50" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U50" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="V50" t="n">
-        <v>43.90243902439025</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>108</v>
+        <v>403</v>
       </c>
       <c r="B51" t="n">
-        <v>-1.243608889519273</v>
+        <v>-0.405771588518279</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1612460207231302</v>
+        <v>0.006916272101322818</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2362146249269394</v>
+        <v>0.3737724590542688</v>
       </c>
       <c r="E51" t="n">
-        <v>18.78900309551608</v>
+        <v>17.98215296844312</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1145670920458298</v>
+        <v>0.1057773704026066</v>
       </c>
       <c r="G51" t="n">
         <v>-0.25</v>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>(164, 58)</t>
+          <t>(170, 20)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4408,54 +4408,54 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.710511127853188</v>
+        <v>14.29398624764567</v>
       </c>
       <c r="O51" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P51" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q51" t="n">
         <v>46</v>
       </c>
       <c r="R51" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="S51" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="T51" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="U51" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="V51" t="n">
-        <v>40.85365853658536</v>
+        <v>42.94117647058823</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>52</v>
+        <v>349</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.5561472294298224</v>
+        <v>-0.9903126303378055</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1035978588354408</v>
+        <v>-0.3078951572810193</v>
       </c>
       <c r="D52" t="n">
-        <v>0.09077297839726156</v>
+        <v>-0.1172225782950266</v>
       </c>
       <c r="E52" t="n">
-        <v>17.33050636288858</v>
+        <v>15.24128225196317</v>
       </c>
       <c r="F52" t="n">
-        <v>0.105673819285906</v>
+        <v>0.08965460148213629</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4477,63 +4477,63 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>(164, 22)</t>
+          <t>(170, 46)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.020038642437223</v>
+        <v>1.291185487533692</v>
       </c>
       <c r="O52" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P52" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q52" t="n">
         <v>46</v>
       </c>
       <c r="R52" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="S52" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="T52" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="U52" t="n">
         <v>72</v>
       </c>
       <c r="V52" t="n">
-        <v>43.90243902439025</v>
+        <v>42.35294117647059</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.405771588518279</v>
+        <v>-0.7679961303828361</v>
       </c>
       <c r="C53" t="n">
-        <v>0.006916272101322107</v>
+        <v>-0.4944564180176811</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3737724590542678</v>
+        <v>-0.1466955793706616</v>
       </c>
       <c r="E53" t="n">
-        <v>15.96291716477452</v>
+        <v>14.53134702148235</v>
       </c>
       <c r="F53" t="n">
-        <v>0.09733486076082026</v>
+        <v>0.08547851189107263</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4555,63 +4555,63 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>(164, 20)</t>
+          <t>(170, 57)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>13.07331280997661</v>
+        <v>1.172873702871051</v>
       </c>
       <c r="O53" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P53" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q53" t="n">
         <v>46</v>
       </c>
       <c r="R53" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S53" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="T53" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="U53" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="V53" t="n">
-        <v>42.68292682926829</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>266</v>
+        <v>151</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.7758626451074774</v>
+        <v>-1.015718323821463</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1182133642912416</v>
+        <v>-0.2801829888464317</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.009053932276387778</v>
+        <v>0.1307557621807462</v>
       </c>
       <c r="E54" t="n">
-        <v>12.69391904540814</v>
+        <v>13.66944884556665</v>
       </c>
       <c r="F54" t="n">
-        <v>0.07740194539883011</v>
+        <v>0.08040852262098029</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4633,63 +4633,63 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>(164, 53)</t>
+          <t>(170, 8)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.654764762536792</v>
+        <v>1.286985740826158</v>
       </c>
       <c r="O54" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P54" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q54" t="n">
         <v>46</v>
       </c>
       <c r="R54" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="S54" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T54" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="U54" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V54" t="n">
-        <v>43.29268292682926</v>
+        <v>42.35294117647059</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.9903126303378055</v>
+        <v>-0.4166751136564736</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.3078951572810193</v>
+        <v>-0.2248018829579642</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.1172225782950266</v>
+        <v>0.04710889322561115</v>
       </c>
       <c r="E55" t="n">
-        <v>11.5049744484794</v>
+        <v>10.84769969830565</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07015228322243537</v>
+        <v>0.06380999822532733</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>(164, 46)</t>
+          <t>(170, 13)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4720,54 +4720,54 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.227844711303486</v>
+        <v>1.283849927703938</v>
       </c>
       <c r="O55" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P55" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q55" t="n">
         <v>46</v>
       </c>
       <c r="R55" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S55" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="T55" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="U55" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="V55" t="n">
-        <v>42.07317073170731</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>241</v>
+        <v>42</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.6331866780480209</v>
+        <v>-1.076375845408949</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3301951787858859</v>
+        <v>-0.1092389015885219</v>
       </c>
       <c r="D56" t="n">
-        <v>0.04546149420378318</v>
+        <v>0.1122752498273479</v>
       </c>
       <c r="E56" t="n">
-        <v>10.08204879053021</v>
+        <v>9.915244173468835</v>
       </c>
       <c r="F56" t="n">
-        <v>0.06147590725933054</v>
+        <v>0.05832496572628727</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>(164, 59)</t>
+          <t>(170, 51)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4798,51 +4798,51 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.186180511433798</v>
+        <v>1.533921202777964</v>
       </c>
       <c r="O56" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q56" t="n">
         <v>46</v>
       </c>
       <c r="R56" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S56" t="n">
         <v>77</v>
       </c>
       <c r="T56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="U56" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="V56" t="n">
-        <v>45.1219512195122</v>
+        <v>40.58823529411764</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.4166751136564736</v>
+        <v>0.00737776448490763</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2248018829579642</v>
+        <v>-0.2337974436379267</v>
       </c>
       <c r="D57" t="n">
-        <v>0.04710889322561115</v>
+        <v>0.07696117327230098</v>
       </c>
       <c r="E57" t="n">
-        <v>9.746934245733442</v>
+        <v>9.335267914370846</v>
       </c>
       <c r="F57" t="n">
-        <v>0.05943252588861855</v>
+        <v>0.05491334067276968</v>
       </c>
       <c r="G57" t="n">
         <v>-0.5</v>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>(164, 13)</t>
+          <t>(170, 67)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4876,54 +4876,54 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.264377349097791</v>
+        <v>1.234875710436817</v>
       </c>
       <c r="O57" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P57" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q57" t="n">
         <v>46</v>
       </c>
       <c r="R57" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="S57" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T57" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="U57" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="V57" t="n">
-        <v>43.90243902439025</v>
+        <v>44.70588235294118</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>239</v>
+        <v>440</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.9653765064458946</v>
+        <v>-0.8603478616594513</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3682009005837906</v>
+        <v>-0.1289120224621031</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.03528075676553887</v>
+        <v>0.06939605158778515</v>
       </c>
       <c r="E58" t="n">
-        <v>8.443454767324312</v>
+        <v>8.675542713713867</v>
       </c>
       <c r="F58" t="n">
-        <v>0.05148448028856287</v>
+        <v>0.05103260419831687</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4945,40 +4945,40 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>(164, 25)</t>
+          <t>(170, 24)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.139827143841672</v>
+        <v>1.395871565922559</v>
       </c>
       <c r="O58" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P58" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q58" t="n">
         <v>46</v>
       </c>
       <c r="R58" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="S58" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="T58" t="n">
         <v>12</v>
       </c>
       <c r="U58" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V58" t="n">
-        <v>42.68292682926829</v>
+        <v>40.58823529411764</v>
       </c>
     </row>
     <row r="59">
@@ -4992,13 +4992,13 @@
         <v>0.01539202612787221</v>
       </c>
       <c r="D59" t="n">
-        <v>0.030376547191606</v>
+        <v>0.0303765471916059</v>
       </c>
       <c r="E59" t="n">
-        <v>7.741970775736235</v>
+        <v>5.964068944954661</v>
       </c>
       <c r="F59" t="n">
-        <v>0.04720713887644046</v>
+        <v>0.0350827584997333</v>
       </c>
       <c r="G59" t="n">
         <v>-0.25</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>(164, 52)</t>
+          <t>(170, 52)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5032,54 +5032,54 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.06698666467027</v>
+        <v>1.279281376491733</v>
       </c>
       <c r="O59" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P59" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q59" t="n">
         <v>46</v>
       </c>
       <c r="R59" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="S59" t="n">
         <v>66</v>
       </c>
       <c r="T59" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U59" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="V59" t="n">
-        <v>41.46341463414634</v>
+        <v>41.17647058823529</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>42</v>
+        <v>421</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.076375845408949</v>
+        <v>-0.1441067751675308</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1092389015885219</v>
+        <v>-0.0609423894753607</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1122752498273479</v>
+        <v>0.0231379903425209</v>
       </c>
       <c r="E60" t="n">
-        <v>7.628725466904456</v>
+        <v>5.881245477392866</v>
       </c>
       <c r="F60" t="n">
-        <v>0.04651661870063693</v>
+        <v>0.03459556163172274</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>(164, 51)</t>
+          <t>(170, 80)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5110,51 +5110,51 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.425824665244754</v>
+        <v>1.567676488065994</v>
       </c>
       <c r="O60" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P60" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
       </c>
       <c r="R60" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="S60" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="T60" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="U60" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="V60" t="n">
-        <v>40.2439024390244</v>
+        <v>41.76470588235294</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.5132171464903902</v>
+        <v>-0.07014857349597037</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1331306902440414</v>
+        <v>0.0168130122842031</v>
       </c>
       <c r="D61" t="n">
-        <v>0.02517308784383725</v>
+        <v>0.03807820395306635</v>
       </c>
       <c r="E61" t="n">
-        <v>6.742369823056364</v>
+        <v>5.817093941746265</v>
       </c>
       <c r="F61" t="n">
-        <v>0.04111201111619735</v>
+        <v>0.03421819965733097</v>
       </c>
       <c r="G61" t="n">
         <v>-0.5</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5179,63 +5179,63 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>(164, 40)</t>
+          <t>(170, 27)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.308809419081619</v>
+        <v>1.035221236915479</v>
       </c>
       <c r="O61" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P61" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q61" t="n">
         <v>46</v>
       </c>
       <c r="R61" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="S61" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="T61" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="U61" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="V61" t="n">
-        <v>45.73170731707317</v>
+        <v>45.29411764705883</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>342</v>
+        <v>120</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.4926726584283918</v>
+        <v>-0.0181093772905345</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.009564310268742134</v>
+        <v>-0.003588587304741679</v>
       </c>
       <c r="D62" t="n">
-        <v>0.08861678450758859</v>
+        <v>0.01589135149311251</v>
       </c>
       <c r="E62" t="n">
-        <v>6.677568409124973</v>
+        <v>5.366925576963368</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04071688054344496</v>
+        <v>0.0315701504527257</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5257,63 +5257,63 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>(164, 22)</t>
+          <t>(170, 22)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>5.257168514964948</v>
+        <v>9.797375616586327</v>
       </c>
       <c r="O62" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P62" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q62" t="n">
         <v>46</v>
       </c>
       <c r="R62" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="S62" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="T62" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="U62" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V62" t="n">
-        <v>43.90243902439025</v>
+        <v>42.94117647058823</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>22</v>
+        <v>458</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.8907288732081902</v>
+        <v>-0.02708422157884229</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3582422798826891</v>
+        <v>0.02504419552587677</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2147455038058414</v>
+        <v>0.03530180783394835</v>
       </c>
       <c r="E63" t="n">
-        <v>5.231285229762435</v>
+        <v>5.199879699180627</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03189808066928314</v>
+        <v>0.03058752764223898</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>(164, 30)</t>
+          <t>(170, 19)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5344,51 +5344,51 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.089040524975803</v>
+        <v>0.2213419916257479</v>
       </c>
       <c r="O63" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P63" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q63" t="n">
         <v>46</v>
       </c>
       <c r="R63" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="S63" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="T63" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="U63" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V63" t="n">
-        <v>43.90243902439025</v>
+        <v>42.94117647058823</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.07014857349597037</v>
+        <v>-0.04442299726246063</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0168130122842031</v>
+        <v>-0.006786055072693813</v>
       </c>
       <c r="D64" t="n">
-        <v>0.03807820395306644</v>
+        <v>0.04153754708303372</v>
       </c>
       <c r="E64" t="n">
-        <v>4.845821101035952</v>
+        <v>4.708418718135775</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02954768964046312</v>
+        <v>0.02769658069491632</v>
       </c>
       <c r="G64" t="n">
         <v>-0.5</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>(164, 27)</t>
+          <t>(170, 59)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5422,51 +5422,51 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.7574298490357418</v>
+        <v>5.081396392782561</v>
       </c>
       <c r="O64" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P64" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q64" t="n">
         <v>46</v>
       </c>
       <c r="R64" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S64" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T64" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U64" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V64" t="n">
-        <v>45.1219512195122</v>
+        <v>44.70588235294118</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.1012540562247923</v>
+        <v>-0.1074515057394339</v>
       </c>
       <c r="C65" t="n">
-        <v>0.01695092044864154</v>
+        <v>-0.04979408540083824</v>
       </c>
       <c r="D65" t="n">
-        <v>0.03201975492241568</v>
+        <v>0.0001656005157713972</v>
       </c>
       <c r="E65" t="n">
-        <v>4.638733928505729</v>
+        <v>4.439551446151896</v>
       </c>
       <c r="F65" t="n">
-        <v>0.02828496297869347</v>
+        <v>0.02611500850677586</v>
       </c>
       <c r="G65" t="n">
         <v>-0.5</v>
@@ -5491,63 +5491,63 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>(164, 16)</t>
+          <t>(170, 26)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.6686387659237851</v>
+        <v>1.524460049753946</v>
       </c>
       <c r="O65" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P65" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q65" t="n">
         <v>46</v>
       </c>
       <c r="R65" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="S65" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="T65" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="U65" t="n">
         <v>73</v>
       </c>
       <c r="V65" t="n">
-        <v>44.51219512195122</v>
+        <v>42.94117647058823</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>118</v>
+        <v>360</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.09132154938169236</v>
+        <v>-0.07787493568228854</v>
       </c>
       <c r="C66" t="n">
-        <v>0.006913329111136904</v>
+        <v>0.004261034975744309</v>
       </c>
       <c r="D66" t="n">
-        <v>0.02476282169742925</v>
+        <v>-0.009257158664772096</v>
       </c>
       <c r="E66" t="n">
-        <v>3.981042102070575</v>
+        <v>4.076199585680811</v>
       </c>
       <c r="F66" t="n">
-        <v>0.02427464696384497</v>
+        <v>0.02397764462165183</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5569,40 +5569,40 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>(164, 44)</t>
+          <t>(170, 26)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.511281840284467</v>
+        <v>4.627187938644758</v>
       </c>
       <c r="O66" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P66" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q66" t="n">
         <v>46</v>
       </c>
       <c r="R66" t="n">
+        <v>83</v>
+      </c>
+      <c r="S66" t="n">
         <v>70</v>
       </c>
-      <c r="S66" t="n">
-        <v>81</v>
-      </c>
       <c r="T66" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U66" t="n">
         <v>71</v>
       </c>
       <c r="V66" t="n">
-        <v>43.29268292682926</v>
+        <v>41.76470588235294</v>
       </c>
     </row>
   </sheetData>
